--- a/BUGS Reportados SIR 2024.xlsx
+++ b/BUGS Reportados SIR 2024.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupokfc-my.sharepoint.com/personal/stephanie_molina_kfc_com_ec/Documents/SIR/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6119" documentId="8_{43C10DBE-7BB1-48C7-8210-269E63AB3D32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AE956A34-C94D-4421-9C0C-87C828A04869}"/>
+  <xr:revisionPtr revIDLastSave="6532" documentId="8_{43C10DBE-7BB1-48C7-8210-269E63AB3D32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4D151825-60F4-47BD-849A-E15D30798EC5}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-3330" windowWidth="29040" windowHeight="15720" xr2:uid="{350FE263-8C04-4D4A-AAD5-30558A5D3A43}"/>
   </bookViews>
@@ -22,7 +22,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Ecommerce!$A$1:$O$28</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">MXP!$A$1:$Q$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">SIR!$A$1:$V$186</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">SIR!$A$1:$V$209</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -150,7 +150,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1772" uniqueCount="477">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1898" uniqueCount="504">
   <si>
     <t>#</t>
   </si>
@@ -1215,22 +1215,94 @@
     <t>Duplicidad al dar clic en el botón guardar compras</t>
   </si>
   <si>
+    <t>reporte de aceite quemado</t>
+  </si>
+  <si>
+    <t>Compras Caja Chica</t>
+  </si>
+  <si>
+    <t>Guías de Despacho Genéricos</t>
+  </si>
+  <si>
+    <t>Cupones Digitales</t>
+  </si>
+  <si>
+    <t>Ordenes de Pedido V2</t>
+  </si>
+  <si>
     <t>Escalado a desarrollo</t>
   </si>
   <si>
-    <t>reporte de aceite quemado</t>
-  </si>
-  <si>
-    <t>Compras Caja Chica</t>
-  </si>
-  <si>
-    <t>Guías de Despacho Genéricos</t>
-  </si>
-  <si>
-    <t>Cupones Digitales</t>
-  </si>
-  <si>
-    <t>Ordenes de Pedido V2</t>
+    <t>Cierre Cajas - Campaña Solidaria</t>
+  </si>
+  <si>
+    <t>administracion de articulos regional</t>
+  </si>
+  <si>
+    <t>70577 </t>
+  </si>
+  <si>
+    <t>CO | Cupones de dinero</t>
+  </si>
+  <si>
+    <t>victor restrepo</t>
+  </si>
+  <si>
+    <t>Cierre Cajas - Campaña Solidaria en el Valor de Sobrantes o Faltantes</t>
+  </si>
+  <si>
+    <t>Gastos Caja Chica V2 - Valor menor a $1 rechazado</t>
+  </si>
+  <si>
+    <t>78290 </t>
+  </si>
+  <si>
+    <t>Gastos Caja Chica V2 - Part 2</t>
+  </si>
+  <si>
+    <t>Orden de Pedidos Error SQL</t>
+  </si>
+  <si>
+    <t>CL | ordenes de pedido v2</t>
+  </si>
+  <si>
+    <t>COL | Cupones de Nómina</t>
+  </si>
+  <si>
+    <t>RE | MOVINV - ERROR EDI_CONFIRMATION NOT NULL</t>
+  </si>
+  <si>
+    <t>Alejandro Guiterrez</t>
+  </si>
+  <si>
+    <t>RE | gastos caja chica  comprobante</t>
+  </si>
+  <si>
+    <t>verision</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EC | activos fijos trasnfrencias </t>
+  </si>
+  <si>
+    <t>amanda taimal</t>
+  </si>
+  <si>
+    <t>Ecuador,Colombia,Venezuela</t>
+  </si>
+  <si>
+    <t>RE | Ordenes de Pedidos V2</t>
+  </si>
+  <si>
+    <t>Andres Valencia,Vanesa Soria</t>
+  </si>
+  <si>
+    <t>EC | Correo de pedidos tesalia</t>
+  </si>
+  <si>
+    <t>CH | ÓRDENES DE PEDIDOS V2- ASENTADO AUTOMÁTICO Y CÓDIGO ERP</t>
+  </si>
+  <si>
+    <t>Diario ERP - Exportación Inventarios</t>
   </si>
   <si>
     <t>1.18.4</t>
@@ -1603,13 +1675,22 @@
   </si>
   <si>
     <t>Observacion QA</t>
+  </si>
+  <si>
+    <t>venezuela</t>
+  </si>
+  <si>
+    <t>VE | Transferencia negativas cupones nomina</t>
+  </si>
+  <si>
+    <t>alejandro guiterrez</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="19">
+  <fonts count="16">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1683,12 +1764,6 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="13"/>
-      <color rgb="FF000000"/>
-      <name val="Segoe UI VSS (Regular)"/>
-      <charset val="1"/>
-    </font>
-    <font>
       <b/>
       <sz val="10"/>
       <color theme="1"/>
@@ -1720,19 +1795,6 @@
       <color rgb="FF000000"/>
       <name val="Bahnschrift Light"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Rubik"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Inter"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="8">
@@ -1779,7 +1841,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="22">
+  <borders count="24">
     <border>
       <left/>
       <right/>
@@ -2003,38 +2065,64 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </left>
       <right/>
       <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
     <border>
       <left/>
-      <right style="thin">
+      <right/>
+      <top/>
+      <bottom style="thin">
         <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="111">
+  <cellXfs count="105">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2287,46 +2375,46 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="84">
+  <dxfs count="92">
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -2757,6 +2845,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C5700"/>
       </font>
       <fill>
@@ -2782,6 +2880,26 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2935,6 +3053,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C5700"/>
       </font>
       <fill>
@@ -2974,6 +3102,40 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3053,6 +3215,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C5700"/>
       </font>
       <fill>
@@ -3068,16 +3240,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3098,10 +3260,10 @@
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="Estilo de tabla dinámica 1" table="0" count="1" xr9:uid="{FE874725-B3DB-4CC6-8844-A83371832CBC}">
-      <tableStyleElement type="wholeTable" dxfId="83"/>
+      <tableStyleElement type="wholeTable" dxfId="91"/>
     </tableStyle>
     <tableStyle name="Estilo de tabla dinámica 2" table="0" count="1" xr9:uid="{817A6582-4704-41AF-A46E-81A9D2717E99}">
-      <tableStyleElement type="pageFieldLabels" dxfId="82"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="90"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -3494,26 +3656,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51912A95-8495-48EF-8281-9EA7F885C6C0}">
   <sheetPr codeName="Hoja1" filterMode="1"/>
-  <dimension ref="A1:AK262"/>
+  <dimension ref="A1:AU248"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="21" customWidth="1"/>
-    <col min="2" max="2" width="9" style="21" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="3.5703125" style="21" customWidth="1"/>
-    <col min="4" max="4" width="9.28515625" style="21" customWidth="1"/>
-    <col min="5" max="5" width="18.7109375" style="21" customWidth="1"/>
-    <col min="6" max="6" width="14.28515625" style="21" customWidth="1"/>
-    <col min="7" max="7" width="10.28515625" style="21" customWidth="1"/>
-    <col min="8" max="8" width="20.28515625" style="21" customWidth="1"/>
-    <col min="9" max="9" width="39" style="34" customWidth="1"/>
-    <col min="10" max="10" width="14.140625" style="33" customWidth="1"/>
-    <col min="11" max="11" width="14.140625" style="21" customWidth="1"/>
-    <col min="12" max="12" width="13.7109375" style="21" customWidth="1"/>
-    <col min="13" max="13" width="15.42578125" style="22" hidden="1" customWidth="1"/>
-    <col min="14" max="14" width="21.28515625" style="21" customWidth="1"/>
-    <col min="15" max="15" width="15.7109375" style="94" customWidth="1"/>
-    <col min="16" max="16" width="9.5703125" style="21" customWidth="1"/>
-    <col min="17" max="17" width="41" style="21" customWidth="1"/>
+    <col min="2" max="2" width="9" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="3.5703125" style="5" customWidth="1"/>
+    <col min="4" max="4" width="9.28515625" style="5" customWidth="1"/>
+    <col min="5" max="5" width="18.7109375" style="5" customWidth="1"/>
+    <col min="6" max="6" width="14.28515625" style="5" customWidth="1"/>
+    <col min="7" max="7" width="10.28515625" style="5" customWidth="1"/>
+    <col min="8" max="8" width="20.28515625" style="5" customWidth="1"/>
+    <col min="9" max="9" width="39" style="11" customWidth="1"/>
+    <col min="10" max="11" width="14.140625" style="5" customWidth="1"/>
+    <col min="12" max="12" width="13.7109375" style="5" customWidth="1"/>
+    <col min="13" max="13" width="15.42578125" style="33" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="33" style="5" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.7109375" style="97" customWidth="1"/>
+    <col min="16" max="16" width="9.5703125" style="5" customWidth="1"/>
+    <col min="17" max="17" width="41" style="5" customWidth="1"/>
     <col min="18" max="18" width="15.28515625" style="21" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="19.140625" style="34" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="61.140625" style="21" hidden="1" customWidth="1"/>
@@ -3523,7 +3684,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" s="17" customFormat="1" ht="38.25" customHeight="1">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="98" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -3559,13 +3720,13 @@
       <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="81" t="s">
+      <c r="M1" s="99" t="s">
         <v>12</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="91" t="s">
+      <c r="O1" s="90" t="s">
         <v>14</v>
       </c>
       <c r="P1" s="1" t="s">
@@ -3574,7 +3735,7 @@
       <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" s="81" t="s">
         <v>17</v>
       </c>
       <c r="S1" s="1" t="s">
@@ -3643,11 +3804,9 @@
       <c r="B3" s="5">
         <v>2024</v>
       </c>
-      <c r="C3" s="5"/>
       <c r="D3" s="5">
         <v>1</v>
       </c>
-      <c r="E3" s="5"/>
       <c r="F3" s="5">
         <v>1</v>
       </c>
@@ -3667,6 +3826,7 @@
       <c r="L3" s="9">
         <v>1</v>
       </c>
+      <c r="M3" s="22"/>
       <c r="N3" s="9" t="s">
         <v>25</v>
       </c>
@@ -3686,11 +3846,9 @@
       <c r="B4" s="5">
         <v>2024</v>
       </c>
-      <c r="C4" s="5"/>
       <c r="D4" s="5">
         <v>3</v>
       </c>
-      <c r="E4" s="5"/>
       <c r="F4" s="9">
         <v>1</v>
       </c>
@@ -3710,6 +3868,7 @@
       <c r="L4" s="9">
         <v>1</v>
       </c>
+      <c r="M4" s="22"/>
       <c r="N4" s="9" t="s">
         <v>25</v>
       </c>
@@ -3729,9 +3888,6 @@
       <c r="B5" s="5">
         <v>2024</v>
       </c>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
       <c r="F5" s="5">
         <v>1</v>
       </c>
@@ -3751,6 +3907,7 @@
       <c r="L5" s="9">
         <v>1</v>
       </c>
+      <c r="M5" s="22"/>
       <c r="N5" s="9" t="s">
         <v>25</v>
       </c>
@@ -3770,9 +3927,6 @@
       <c r="B6" s="5">
         <v>2024</v>
       </c>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
       <c r="F6" s="9">
         <v>1</v>
       </c>
@@ -3792,6 +3946,7 @@
       <c r="L6" s="9">
         <v>1</v>
       </c>
+      <c r="M6" s="22"/>
       <c r="N6" s="9" t="s">
         <v>25</v>
       </c>
@@ -3811,9 +3966,6 @@
       <c r="B7" s="5">
         <v>2024</v>
       </c>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
       <c r="F7" s="5">
         <v>1</v>
       </c>
@@ -3833,6 +3985,7 @@
       <c r="L7" s="9">
         <v>1</v>
       </c>
+      <c r="M7" s="22"/>
       <c r="N7" s="9" t="s">
         <v>25</v>
       </c>
@@ -3850,11 +4003,9 @@
       <c r="B8" s="5">
         <v>2024</v>
       </c>
-      <c r="C8" s="5"/>
       <c r="D8" s="5">
         <v>2</v>
       </c>
-      <c r="E8" s="5"/>
       <c r="F8" s="9">
         <v>1</v>
       </c>
@@ -3902,9 +4053,6 @@
       <c r="B9" s="5">
         <v>2024</v>
       </c>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
       <c r="F9" s="5">
         <v>1</v>
       </c>
@@ -3924,6 +4072,7 @@
       <c r="L9" s="9">
         <v>1</v>
       </c>
+      <c r="M9" s="22"/>
       <c r="N9" s="9" t="s">
         <v>25</v>
       </c>
@@ -3941,9 +4090,6 @@
       <c r="B10" s="5">
         <v>2024</v>
       </c>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
       <c r="F10" s="9">
         <v>1</v>
       </c>
@@ -3985,9 +4131,6 @@
       <c r="B11" s="5">
         <v>2024</v>
       </c>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
       <c r="F11" s="5">
         <v>1</v>
       </c>
@@ -4007,6 +4150,7 @@
       <c r="L11" s="9">
         <v>1</v>
       </c>
+      <c r="M11" s="22"/>
       <c r="N11" s="9" t="s">
         <v>25</v>
       </c>
@@ -4026,9 +4170,6 @@
       <c r="B12" s="5">
         <v>2024</v>
       </c>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
       <c r="F12" s="9">
         <v>1</v>
       </c>
@@ -4070,9 +4211,6 @@
       <c r="B13" s="5">
         <v>2024</v>
       </c>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
       <c r="F13" s="5">
         <v>1</v>
       </c>
@@ -4116,9 +4254,6 @@
       <c r="B14" s="5">
         <v>2024</v>
       </c>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
       <c r="F14" s="9">
         <v>1</v>
       </c>
@@ -4158,9 +4293,6 @@
       <c r="B15" s="5">
         <v>2024</v>
       </c>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
       <c r="F15" s="5">
         <v>1</v>
       </c>
@@ -4204,9 +4336,6 @@
       <c r="B16" s="5">
         <v>2024</v>
       </c>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
       <c r="F16" s="9">
         <v>1</v>
       </c>
@@ -4248,11 +4377,9 @@
       <c r="B17" s="5">
         <v>2024</v>
       </c>
-      <c r="C17" s="5"/>
       <c r="D17" s="5">
         <v>3</v>
       </c>
-      <c r="E17" s="5"/>
       <c r="F17" s="5">
         <v>1</v>
       </c>
@@ -4292,9 +4419,6 @@
       <c r="B18" s="5">
         <v>2024</v>
       </c>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
       <c r="F18" s="9">
         <v>1</v>
       </c>
@@ -4310,6 +4434,7 @@
       <c r="J18" s="28" t="s">
         <v>24</v>
       </c>
+      <c r="K18" s="21"/>
       <c r="L18" s="9">
         <v>1</v>
       </c>
@@ -4333,9 +4458,6 @@
       <c r="B19" s="5">
         <v>2024</v>
       </c>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
       <c r="F19" s="5">
         <v>1</v>
       </c>
@@ -4377,9 +4499,6 @@
       <c r="B20" s="5">
         <v>2024</v>
       </c>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
-      <c r="E20" s="5"/>
       <c r="F20" s="9">
         <v>1</v>
       </c>
@@ -4423,9 +4542,6 @@
       <c r="B21" s="5">
         <v>2024</v>
       </c>
-      <c r="C21" s="5"/>
-      <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
       <c r="F21" s="5">
         <v>1</v>
       </c>
@@ -4474,8 +4590,6 @@
       <c r="C22" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
       <c r="F22" s="9">
         <v>1</v>
       </c>
@@ -4525,7 +4639,6 @@
       <c r="D23" s="5">
         <v>1</v>
       </c>
-      <c r="E23" s="5"/>
       <c r="F23" s="5">
         <v>1</v>
       </c>
@@ -4569,11 +4682,9 @@
       <c r="B24" s="5">
         <v>2024</v>
       </c>
-      <c r="C24" s="5"/>
       <c r="D24" s="5">
         <v>1</v>
       </c>
-      <c r="E24" s="5"/>
       <c r="F24" s="9">
         <v>1</v>
       </c>
@@ -4617,9 +4728,6 @@
       <c r="B25" s="5">
         <v>2024</v>
       </c>
-      <c r="C25" s="5"/>
-      <c r="D25" s="5"/>
-      <c r="E25" s="5"/>
       <c r="F25" s="5">
         <v>1</v>
       </c>
@@ -4663,9 +4771,6 @@
       <c r="B26" s="5">
         <v>2024</v>
       </c>
-      <c r="C26" s="5"/>
-      <c r="D26" s="5"/>
-      <c r="E26" s="5"/>
       <c r="F26" s="9">
         <v>1</v>
       </c>
@@ -4709,11 +4814,9 @@
       <c r="B27" s="5">
         <v>2024</v>
       </c>
-      <c r="C27" s="5"/>
       <c r="D27" s="5">
         <v>2</v>
       </c>
-      <c r="E27" s="5"/>
       <c r="F27" s="5">
         <v>2</v>
       </c>
@@ -4765,7 +4868,6 @@
       <c r="D28" s="5">
         <v>1</v>
       </c>
-      <c r="E28" s="5"/>
       <c r="F28" s="5">
         <v>2</v>
       </c>
@@ -4811,11 +4913,9 @@
       <c r="B29" s="5">
         <v>2024</v>
       </c>
-      <c r="C29" s="5"/>
       <c r="D29" s="5">
         <v>2</v>
       </c>
-      <c r="E29" s="5"/>
       <c r="F29" s="5">
         <v>2</v>
       </c>
@@ -4867,7 +4967,6 @@
       <c r="D30" s="5">
         <v>2</v>
       </c>
-      <c r="E30" s="5"/>
       <c r="F30" s="5">
         <v>2</v>
       </c>
@@ -4913,11 +5012,9 @@
       <c r="B31" s="5">
         <v>2024</v>
       </c>
-      <c r="C31" s="5"/>
       <c r="D31" s="5">
         <v>1</v>
       </c>
-      <c r="E31" s="5"/>
       <c r="F31" s="5">
         <v>2</v>
       </c>
@@ -4967,7 +5064,6 @@
       <c r="D32" s="5">
         <v>2</v>
       </c>
-      <c r="E32" s="5"/>
       <c r="F32" s="5">
         <v>2</v>
       </c>
@@ -5013,11 +5109,9 @@
       <c r="B33" s="5">
         <v>2024</v>
       </c>
-      <c r="C33" s="5"/>
       <c r="D33" s="5">
         <v>1</v>
       </c>
-      <c r="E33" s="5"/>
       <c r="F33" s="5">
         <v>2</v>
       </c>
@@ -5063,11 +5157,9 @@
       <c r="B34" s="5">
         <v>2024</v>
       </c>
-      <c r="C34" s="5"/>
       <c r="D34" s="5">
         <v>1</v>
       </c>
-      <c r="E34" s="5"/>
       <c r="F34" s="5">
         <v>2</v>
       </c>
@@ -5115,7 +5207,6 @@
       <c r="D35" s="5">
         <v>3</v>
       </c>
-      <c r="E35" s="5"/>
       <c r="F35" s="5">
         <v>2</v>
       </c>
@@ -5159,11 +5250,9 @@
       <c r="B36" s="5">
         <v>2024</v>
       </c>
-      <c r="C36" s="5"/>
       <c r="D36" s="5">
         <v>2</v>
       </c>
-      <c r="E36" s="5"/>
       <c r="F36" s="5">
         <v>2</v>
       </c>
@@ -5213,7 +5302,6 @@
       <c r="D37" s="5">
         <v>2</v>
       </c>
-      <c r="E37" s="5"/>
       <c r="F37" s="5">
         <v>2</v>
       </c>
@@ -5265,7 +5353,6 @@
       <c r="D38" s="5">
         <v>2</v>
       </c>
-      <c r="E38" s="5"/>
       <c r="F38" s="5">
         <v>2</v>
       </c>
@@ -5309,11 +5396,9 @@
       <c r="B39" s="5">
         <v>2024</v>
       </c>
-      <c r="C39" s="5"/>
       <c r="D39" s="5">
         <v>2</v>
       </c>
-      <c r="E39" s="5"/>
       <c r="F39" s="5">
         <v>3</v>
       </c>
@@ -5363,11 +5448,9 @@
       <c r="B40" s="5">
         <v>2024</v>
       </c>
-      <c r="C40" s="5"/>
       <c r="D40" s="5">
         <v>3</v>
       </c>
-      <c r="E40" s="5"/>
       <c r="F40" s="5">
         <v>3</v>
       </c>
@@ -5413,11 +5496,9 @@
       <c r="B41" s="5">
         <v>2024</v>
       </c>
-      <c r="C41" s="5"/>
       <c r="D41" s="5">
         <v>2</v>
       </c>
-      <c r="E41" s="5"/>
       <c r="F41" s="5">
         <v>3</v>
       </c>
@@ -5461,11 +5542,9 @@
       <c r="B42" s="5">
         <v>2024</v>
       </c>
-      <c r="C42" s="5"/>
       <c r="D42" s="5">
         <v>1</v>
       </c>
-      <c r="E42" s="5"/>
       <c r="F42" s="5">
         <v>3</v>
       </c>
@@ -5505,11 +5584,9 @@
       <c r="B43" s="5">
         <v>2024</v>
       </c>
-      <c r="C43" s="5"/>
       <c r="D43" s="5">
         <v>1</v>
       </c>
-      <c r="E43" s="5"/>
       <c r="F43" s="5">
         <v>3</v>
       </c>
@@ -5559,11 +5636,9 @@
       <c r="B44" s="5">
         <v>2024</v>
       </c>
-      <c r="C44" s="5"/>
       <c r="D44" s="5">
         <v>2</v>
       </c>
-      <c r="E44" s="5"/>
       <c r="F44" s="5">
         <v>3</v>
       </c>
@@ -5605,11 +5680,9 @@
       <c r="B45" s="5">
         <v>2024</v>
       </c>
-      <c r="C45" s="5"/>
       <c r="D45" s="5">
         <v>3</v>
       </c>
-      <c r="E45" s="5"/>
       <c r="F45" s="5">
         <v>4</v>
       </c>
@@ -5651,11 +5724,9 @@
       <c r="B46" s="5">
         <v>2024</v>
       </c>
-      <c r="C46" s="5"/>
       <c r="D46" s="5">
         <v>2</v>
       </c>
-      <c r="E46" s="5"/>
       <c r="F46" s="5">
         <v>4</v>
       </c>
@@ -5703,11 +5774,9 @@
       <c r="B47" s="5">
         <v>2024</v>
       </c>
-      <c r="C47" s="5"/>
       <c r="D47" s="5">
         <v>1</v>
       </c>
-      <c r="E47" s="5"/>
       <c r="F47" s="5">
         <v>4</v>
       </c>
@@ -5749,11 +5818,9 @@
       <c r="B48" s="5">
         <v>2024</v>
       </c>
-      <c r="C48" s="5"/>
       <c r="D48" s="5">
         <v>1</v>
       </c>
-      <c r="E48" s="5"/>
       <c r="F48" s="5">
         <v>4</v>
       </c>
@@ -5797,11 +5864,9 @@
       <c r="B49" s="5">
         <v>2024</v>
       </c>
-      <c r="C49" s="5"/>
       <c r="D49" s="5">
         <v>3</v>
       </c>
-      <c r="E49" s="5"/>
       <c r="F49" s="5">
         <v>4</v>
       </c>
@@ -5847,11 +5912,9 @@
       <c r="B50" s="5">
         <v>2024</v>
       </c>
-      <c r="C50" s="5"/>
       <c r="D50" s="5">
         <v>1</v>
       </c>
-      <c r="E50" s="5"/>
       <c r="F50" s="5">
         <v>4</v>
       </c>
@@ -5895,11 +5958,9 @@
       <c r="B51" s="5">
         <v>2024</v>
       </c>
-      <c r="C51" s="5"/>
       <c r="D51" s="5">
         <v>3</v>
       </c>
-      <c r="E51" s="5"/>
       <c r="F51" s="5">
         <v>4</v>
       </c>
@@ -5943,11 +6004,9 @@
       <c r="B52" s="5">
         <v>2024</v>
       </c>
-      <c r="C52" s="5"/>
       <c r="D52" s="5">
         <v>3</v>
       </c>
-      <c r="E52" s="5"/>
       <c r="F52" s="5">
         <v>4</v>
       </c>
@@ -5993,11 +6052,9 @@
       <c r="B53" s="5">
         <v>2024</v>
       </c>
-      <c r="C53" s="5"/>
       <c r="D53" s="5">
         <v>1</v>
       </c>
-      <c r="E53" s="5"/>
       <c r="F53" s="5">
         <v>4</v>
       </c>
@@ -6039,11 +6096,9 @@
       <c r="B54" s="5">
         <v>2024</v>
       </c>
-      <c r="C54" s="5"/>
       <c r="D54" s="5">
         <v>1</v>
       </c>
-      <c r="E54" s="5"/>
       <c r="F54" s="5">
         <v>4</v>
       </c>
@@ -6091,11 +6146,9 @@
       <c r="B55" s="5">
         <v>2024</v>
       </c>
-      <c r="C55" s="5"/>
       <c r="D55" s="5">
         <v>2</v>
       </c>
-      <c r="E55" s="5"/>
       <c r="F55" s="5">
         <v>5</v>
       </c>
@@ -6139,11 +6192,9 @@
       <c r="B56" s="5">
         <v>2024</v>
       </c>
-      <c r="C56" s="5"/>
       <c r="D56" s="5">
         <v>1</v>
       </c>
-      <c r="E56" s="5"/>
       <c r="F56" s="5">
         <v>5</v>
       </c>
@@ -6193,11 +6244,9 @@
       <c r="B57" s="5">
         <v>2024</v>
       </c>
-      <c r="C57" s="5"/>
       <c r="D57" s="5">
         <v>1</v>
       </c>
-      <c r="E57" s="5"/>
       <c r="F57" s="5">
         <v>5</v>
       </c>
@@ -6241,11 +6290,9 @@
       <c r="B58" s="5">
         <v>2024</v>
       </c>
-      <c r="C58" s="5"/>
       <c r="D58" s="5">
         <v>1</v>
       </c>
-      <c r="E58" s="5"/>
       <c r="F58" s="5">
         <v>5</v>
       </c>
@@ -6293,11 +6340,9 @@
       <c r="B59" s="5">
         <v>2024</v>
       </c>
-      <c r="C59" s="5"/>
       <c r="D59" s="5">
         <v>2</v>
       </c>
-      <c r="E59" s="5"/>
       <c r="F59" s="5">
         <v>5</v>
       </c>
@@ -6345,11 +6390,9 @@
       <c r="B60" s="5">
         <v>2024</v>
       </c>
-      <c r="C60" s="5"/>
       <c r="D60" s="5">
         <v>3</v>
       </c>
-      <c r="E60" s="5"/>
       <c r="F60" s="5">
         <v>5</v>
       </c>
@@ -6391,11 +6434,9 @@
       <c r="B61" s="5">
         <v>2024</v>
       </c>
-      <c r="C61" s="5"/>
       <c r="D61" s="5">
         <v>1</v>
       </c>
-      <c r="E61" s="5"/>
       <c r="F61" s="5">
         <v>6</v>
       </c>
@@ -6443,11 +6484,9 @@
       <c r="B62" s="5">
         <v>2024</v>
       </c>
-      <c r="C62" s="5"/>
       <c r="D62" s="5">
         <v>1</v>
       </c>
-      <c r="E62" s="5"/>
       <c r="F62" s="5">
         <v>6</v>
       </c>
@@ -6479,6 +6518,7 @@
       <c r="P62" s="21">
         <v>794294</v>
       </c>
+      <c r="Q62" s="21"/>
       <c r="R62" s="5">
         <v>18000</v>
       </c>
@@ -6494,11 +6534,9 @@
       <c r="B63" s="5">
         <v>2024</v>
       </c>
-      <c r="C63" s="5"/>
       <c r="D63" s="5">
         <v>1</v>
       </c>
-      <c r="E63" s="5"/>
       <c r="F63" s="5">
         <v>6</v>
       </c>
@@ -6546,11 +6584,9 @@
       <c r="B64" s="5">
         <v>2024</v>
       </c>
-      <c r="C64" s="5"/>
       <c r="D64" s="5">
         <v>1</v>
       </c>
-      <c r="E64" s="5"/>
       <c r="F64" s="5">
         <v>6</v>
       </c>
@@ -6598,11 +6634,9 @@
       <c r="B65" s="5">
         <v>2024</v>
       </c>
-      <c r="C65" s="5"/>
       <c r="D65" s="5">
         <v>2</v>
       </c>
-      <c r="E65" s="5"/>
       <c r="F65" s="5">
         <v>6</v>
       </c>
@@ -6648,11 +6682,9 @@
       <c r="B66" s="5">
         <v>2024</v>
       </c>
-      <c r="C66" s="5"/>
       <c r="D66" s="5">
         <v>1</v>
       </c>
-      <c r="E66" s="5"/>
       <c r="F66" s="5">
         <v>6</v>
       </c>
@@ -6694,11 +6726,9 @@
       <c r="B67" s="5">
         <v>2024</v>
       </c>
-      <c r="C67" s="5"/>
       <c r="D67" s="5">
         <v>1</v>
       </c>
-      <c r="E67" s="5"/>
       <c r="F67" s="5">
         <v>6</v>
       </c>
@@ -6730,7 +6760,6 @@
       <c r="P67" s="5">
         <v>795603</v>
       </c>
-      <c r="Q67" s="5"/>
       <c r="R67" s="5">
         <v>5</v>
       </c>
@@ -6746,11 +6775,9 @@
       <c r="B68" s="5">
         <v>2024</v>
       </c>
-      <c r="C68" s="5"/>
       <c r="D68" s="5">
         <v>2</v>
       </c>
-      <c r="E68" s="5"/>
       <c r="F68" s="5">
         <v>7</v>
       </c>
@@ -6782,7 +6809,6 @@
       <c r="P68" s="5">
         <v>794430</v>
       </c>
-      <c r="Q68" s="5"/>
       <c r="R68" s="5"/>
       <c r="S68" s="11"/>
       <c r="T68" s="33"/>
@@ -6794,11 +6820,9 @@
       <c r="B69" s="5">
         <v>2024</v>
       </c>
-      <c r="C69" s="5"/>
       <c r="D69" s="5">
         <v>2</v>
       </c>
-      <c r="E69" s="5"/>
       <c r="F69" s="5">
         <v>7</v>
       </c>
@@ -6830,7 +6854,6 @@
       <c r="P69" s="5">
         <v>799356</v>
       </c>
-      <c r="Q69" s="5"/>
       <c r="R69" s="5">
         <v>4</v>
       </c>
@@ -6846,7 +6869,6 @@
       <c r="B70" s="5">
         <v>2024</v>
       </c>
-      <c r="C70" s="5"/>
       <c r="D70" s="9">
         <v>2</v>
       </c>
@@ -6894,7 +6916,6 @@
       <c r="B71" s="5">
         <v>2024</v>
       </c>
-      <c r="C71" s="5"/>
       <c r="D71" s="9">
         <v>2</v>
       </c>
@@ -6942,11 +6963,9 @@
       <c r="B72" s="5">
         <v>2024</v>
       </c>
-      <c r="C72" s="5"/>
       <c r="D72" s="5">
         <v>1</v>
       </c>
-      <c r="E72" s="5"/>
       <c r="F72" s="5">
         <v>7</v>
       </c>
@@ -6978,7 +6997,6 @@
       <c r="P72" s="5">
         <v>798375</v>
       </c>
-      <c r="Q72" s="5"/>
       <c r="R72" s="5"/>
       <c r="S72" s="11"/>
       <c r="T72" s="33"/>
@@ -6990,7 +7008,6 @@
       <c r="B73" s="5">
         <v>2024</v>
       </c>
-      <c r="C73" s="5"/>
       <c r="D73" s="9">
         <v>2</v>
       </c>
@@ -7038,11 +7055,9 @@
       <c r="B74" s="5">
         <v>2024</v>
       </c>
-      <c r="C74" s="5"/>
       <c r="D74" s="5">
         <v>2</v>
       </c>
-      <c r="E74" s="5"/>
       <c r="F74" s="5">
         <v>6</v>
       </c>
@@ -7138,11 +7153,9 @@
       <c r="B76" s="5">
         <v>2024</v>
       </c>
-      <c r="C76" s="5"/>
       <c r="D76" s="5">
         <v>1</v>
       </c>
-      <c r="E76" s="5"/>
       <c r="F76" s="5">
         <v>7</v>
       </c>
@@ -7171,8 +7184,6 @@
       <c r="O76" s="5">
         <v>32567</v>
       </c>
-      <c r="P76" s="5"/>
-      <c r="Q76" s="5"/>
       <c r="R76" s="5"/>
       <c r="S76" s="11"/>
       <c r="T76" s="33" t="s">
@@ -7186,11 +7197,9 @@
       <c r="B77" s="5">
         <v>2024</v>
       </c>
-      <c r="C77" s="5"/>
       <c r="D77" s="5">
         <v>2</v>
       </c>
-      <c r="E77" s="5"/>
       <c r="F77" s="5">
         <v>7</v>
       </c>
@@ -7222,7 +7231,6 @@
       <c r="P77" s="5">
         <v>800584</v>
       </c>
-      <c r="Q77" s="5"/>
       <c r="R77" s="5">
         <v>3</v>
       </c>
@@ -7244,7 +7252,6 @@
       <c r="D78" s="5">
         <v>3</v>
       </c>
-      <c r="E78" s="5"/>
       <c r="F78" s="5">
         <v>7</v>
       </c>
@@ -7273,8 +7280,6 @@
       <c r="O78" s="5">
         <v>32779</v>
       </c>
-      <c r="P78" s="5"/>
-      <c r="Q78" s="5"/>
       <c r="R78" s="5">
         <v>2</v>
       </c>
@@ -7290,11 +7295,9 @@
       <c r="B79" s="5">
         <v>2024</v>
       </c>
-      <c r="C79" s="5"/>
       <c r="D79" s="5">
         <v>2</v>
       </c>
-      <c r="E79" s="5"/>
       <c r="F79" s="5">
         <v>8</v>
       </c>
@@ -7326,7 +7329,6 @@
       <c r="P79" s="5">
         <v>804843</v>
       </c>
-      <c r="Q79" s="5"/>
       <c r="R79" s="5">
         <v>1</v>
       </c>
@@ -7342,11 +7344,9 @@
       <c r="B80" s="5">
         <v>2024</v>
       </c>
-      <c r="C80" s="5"/>
       <c r="D80" s="5">
         <v>2</v>
       </c>
-      <c r="E80" s="5"/>
       <c r="F80" s="5">
         <v>7</v>
       </c>
@@ -7378,7 +7378,6 @@
       <c r="P80" s="5">
         <v>801024</v>
       </c>
-      <c r="Q80" s="5"/>
       <c r="R80" s="5"/>
       <c r="S80" s="11"/>
       <c r="T80" s="33"/>
@@ -7390,11 +7389,9 @@
       <c r="B81" s="5">
         <v>2024</v>
       </c>
-      <c r="C81" s="5"/>
       <c r="D81" s="5">
         <v>2</v>
       </c>
-      <c r="E81" s="5"/>
       <c r="F81" s="5">
         <v>8</v>
       </c>
@@ -7438,11 +7435,9 @@
       <c r="B82" s="5">
         <v>2024</v>
       </c>
-      <c r="C82" s="5"/>
       <c r="D82" s="5">
         <v>2</v>
       </c>
-      <c r="E82" s="5"/>
       <c r="F82" s="5">
         <v>8</v>
       </c>
@@ -7472,7 +7467,6 @@
       <c r="P82" s="5">
         <v>806521</v>
       </c>
-      <c r="Q82" s="5"/>
       <c r="R82" s="5"/>
       <c r="S82" s="11"/>
       <c r="T82" s="33" t="s">
@@ -7486,11 +7480,9 @@
       <c r="B83" s="5">
         <v>2024</v>
       </c>
-      <c r="C83" s="5"/>
       <c r="D83" s="5">
         <v>2</v>
       </c>
-      <c r="E83" s="5"/>
       <c r="F83" s="5">
         <v>8</v>
       </c>
@@ -7520,7 +7512,6 @@
       <c r="P83" s="5">
         <v>806527</v>
       </c>
-      <c r="Q83" s="5"/>
       <c r="R83" s="5">
         <v>3</v>
       </c>
@@ -7536,11 +7527,9 @@
       <c r="B84" s="5">
         <v>2024</v>
       </c>
-      <c r="C84" s="5"/>
       <c r="D84" s="5">
         <v>2</v>
       </c>
-      <c r="E84" s="5"/>
       <c r="F84" s="5">
         <v>8</v>
       </c>
@@ -7570,7 +7559,6 @@
       <c r="P84" s="5">
         <v>808559</v>
       </c>
-      <c r="Q84" s="5"/>
       <c r="R84" s="5">
         <v>30</v>
       </c>
@@ -7586,11 +7574,9 @@
       <c r="B85" s="5">
         <v>2024</v>
       </c>
-      <c r="C85" s="5"/>
       <c r="D85" s="5">
         <v>2</v>
       </c>
-      <c r="E85" s="5"/>
       <c r="F85" s="5">
         <v>8</v>
       </c>
@@ -7620,7 +7606,6 @@
       <c r="P85" s="5">
         <v>808564</v>
       </c>
-      <c r="Q85" s="5"/>
       <c r="R85" s="5">
         <v>2</v>
       </c>
@@ -7636,11 +7621,9 @@
       <c r="B86" s="5">
         <v>2024</v>
       </c>
-      <c r="C86" s="5"/>
       <c r="D86" s="5">
         <v>2</v>
       </c>
-      <c r="E86" s="5"/>
       <c r="F86" s="5">
         <v>9</v>
       </c>
@@ -7672,7 +7655,6 @@
       <c r="P86" s="5">
         <v>812028</v>
       </c>
-      <c r="Q86" s="5"/>
       <c r="R86" s="5"/>
       <c r="S86" s="11"/>
       <c r="T86" s="33"/>
@@ -7690,7 +7672,6 @@
       <c r="D87" s="5">
         <v>1</v>
       </c>
-      <c r="E87" s="5"/>
       <c r="F87" s="5">
         <v>10</v>
       </c>
@@ -7722,7 +7703,6 @@
       <c r="P87" s="5">
         <v>814658</v>
       </c>
-      <c r="Q87" s="5"/>
       <c r="R87" s="5">
         <v>15</v>
       </c>
@@ -7746,7 +7726,6 @@
       <c r="D88" s="5">
         <v>2</v>
       </c>
-      <c r="E88" s="5"/>
       <c r="F88" s="5">
         <v>10</v>
       </c>
@@ -7778,7 +7757,6 @@
       <c r="P88" s="5">
         <v>814612</v>
       </c>
-      <c r="Q88" s="5"/>
       <c r="R88" s="5">
         <v>2</v>
       </c>
@@ -7794,11 +7772,9 @@
       <c r="B89" s="5">
         <v>2025</v>
       </c>
-      <c r="C89" s="5"/>
       <c r="D89" s="5">
         <v>2</v>
       </c>
-      <c r="E89" s="5"/>
       <c r="F89" s="5">
         <v>10</v>
       </c>
@@ -7844,11 +7820,9 @@
       <c r="B90" s="5">
         <v>2024</v>
       </c>
-      <c r="C90" s="5"/>
       <c r="D90" s="5">
         <v>1</v>
       </c>
-      <c r="E90" s="5"/>
       <c r="F90" s="5">
         <v>7</v>
       </c>
@@ -7873,8 +7847,6 @@
         <v>25</v>
       </c>
       <c r="O90" s="5"/>
-      <c r="P90" s="5"/>
-      <c r="Q90" s="5"/>
       <c r="R90" s="5">
         <v>18600</v>
       </c>
@@ -7895,7 +7867,6 @@
       <c r="D91" s="5">
         <v>2</v>
       </c>
-      <c r="E91" s="5"/>
       <c r="F91" s="5">
         <v>10</v>
       </c>
@@ -7953,7 +7924,6 @@
       <c r="D92" s="5">
         <v>2</v>
       </c>
-      <c r="E92" s="5"/>
       <c r="F92" s="5">
         <v>10</v>
       </c>
@@ -8002,11 +7972,9 @@
       <c r="B93" s="5">
         <v>2025</v>
       </c>
-      <c r="C93" s="5"/>
       <c r="D93" s="5">
         <v>2</v>
       </c>
-      <c r="E93" s="5"/>
       <c r="F93" s="5">
         <v>10</v>
       </c>
@@ -8053,11 +8021,9 @@
       <c r="B94" s="5">
         <v>2025</v>
       </c>
-      <c r="C94" s="5"/>
       <c r="D94" s="5">
         <v>2</v>
       </c>
-      <c r="E94" s="5"/>
       <c r="F94" s="5">
         <v>10</v>
       </c>
@@ -8089,7 +8055,6 @@
       <c r="P94" s="5">
         <v>816427</v>
       </c>
-      <c r="Q94" s="5"/>
       <c r="R94" s="5">
         <v>2</v>
       </c>
@@ -8110,7 +8075,6 @@
       <c r="D95" s="5">
         <v>2</v>
       </c>
-      <c r="E95" s="5"/>
       <c r="F95" s="5">
         <v>10</v>
       </c>
@@ -8137,8 +8101,6 @@
       <c r="O95" s="5">
         <v>47960</v>
       </c>
-      <c r="P95" s="5"/>
-      <c r="Q95" s="5"/>
       <c r="R95" s="5">
         <v>3</v>
       </c>
@@ -8156,11 +8118,9 @@
       <c r="B96" s="5">
         <v>2025</v>
       </c>
-      <c r="C96" s="5"/>
       <c r="D96" s="5">
         <v>3</v>
       </c>
-      <c r="E96" s="5"/>
       <c r="F96" s="5">
         <v>10</v>
       </c>
@@ -8203,11 +8163,9 @@
       <c r="B97" s="5">
         <v>2025</v>
       </c>
-      <c r="C97" s="5"/>
       <c r="D97" s="5">
         <v>2</v>
       </c>
-      <c r="E97" s="5"/>
       <c r="F97" s="5">
         <v>10</v>
       </c>
@@ -8234,8 +8192,6 @@
         <v>25</v>
       </c>
       <c r="O97" s="5"/>
-      <c r="P97" s="5"/>
-      <c r="Q97" s="5"/>
       <c r="R97" s="5"/>
       <c r="S97" s="11"/>
       <c r="T97" s="21" t="s">
@@ -8249,11 +8205,9 @@
       <c r="B98" s="5">
         <v>2025</v>
       </c>
-      <c r="C98" s="5"/>
       <c r="D98" s="5">
         <v>3</v>
       </c>
-      <c r="E98" s="5"/>
       <c r="F98" s="5">
         <v>10</v>
       </c>
@@ -8285,7 +8239,6 @@
       <c r="P98" s="5">
         <v>817129</v>
       </c>
-      <c r="Q98" s="5"/>
       <c r="R98" s="5"/>
       <c r="S98" s="11"/>
     </row>
@@ -8302,7 +8255,6 @@
       <c r="D99" s="5">
         <v>2</v>
       </c>
-      <c r="E99" s="5"/>
       <c r="F99" s="5">
         <v>11</v>
       </c>
@@ -8351,11 +8303,9 @@
       <c r="B100" s="5">
         <v>2025</v>
       </c>
-      <c r="C100" s="5"/>
       <c r="D100" s="5">
         <v>1</v>
       </c>
-      <c r="E100" s="5"/>
       <c r="F100" s="5">
         <v>11</v>
       </c>
@@ -8387,7 +8337,6 @@
       <c r="P100" s="5">
         <v>818067</v>
       </c>
-      <c r="Q100" s="5"/>
       <c r="R100" s="11" t="s">
         <v>181</v>
       </c>
@@ -8451,11 +8400,9 @@
       <c r="B102" s="5">
         <v>2025</v>
       </c>
-      <c r="C102" s="5"/>
       <c r="D102" s="5">
         <v>1</v>
       </c>
-      <c r="E102" s="5"/>
       <c r="F102" s="5">
         <v>11</v>
       </c>
@@ -8474,14 +8421,13 @@
       <c r="K102" s="5">
         <v>15</v>
       </c>
-      <c r="L102" s="5"/>
+      <c r="M102" s="22"/>
       <c r="N102" s="5" t="s">
         <v>186</v>
       </c>
       <c r="O102" s="5">
         <v>53673</v>
       </c>
-      <c r="P102" s="5"/>
       <c r="Q102" s="5" t="s">
         <v>187</v>
       </c>
@@ -8559,7 +8505,6 @@
       <c r="D104" s="5">
         <v>2</v>
       </c>
-      <c r="E104" s="5"/>
       <c r="F104" s="5">
         <v>11</v>
       </c>
@@ -8612,7 +8557,6 @@
       <c r="D105" s="5">
         <v>2</v>
       </c>
-      <c r="E105" s="5"/>
       <c r="F105" s="5">
         <v>12</v>
       </c>
@@ -8665,7 +8609,6 @@
       <c r="D106" s="5">
         <v>2</v>
       </c>
-      <c r="E106" s="5"/>
       <c r="F106" s="5">
         <v>12</v>
       </c>
@@ -8772,7 +8715,6 @@
       <c r="D108" s="5">
         <v>2</v>
       </c>
-      <c r="E108" s="5"/>
       <c r="F108" s="5">
         <v>13</v>
       </c>
@@ -8791,7 +8733,7 @@
       <c r="K108" s="5">
         <v>15</v>
       </c>
-      <c r="L108" s="5"/>
+      <c r="M108" s="22"/>
       <c r="N108" s="5" t="s">
         <v>186</v>
       </c>
@@ -8885,7 +8827,6 @@
       <c r="D110" s="5">
         <v>2</v>
       </c>
-      <c r="E110" s="5"/>
       <c r="F110" s="5">
         <v>13</v>
       </c>
@@ -8933,11 +8874,9 @@
       <c r="B111" s="5">
         <v>2025</v>
       </c>
-      <c r="C111" s="5"/>
       <c r="D111" s="5">
         <v>2</v>
       </c>
-      <c r="E111" s="5"/>
       <c r="F111" s="5">
         <v>13</v>
       </c>
@@ -8991,7 +8930,6 @@
       <c r="D112" s="5">
         <v>3</v>
       </c>
-      <c r="E112" s="5"/>
       <c r="F112" s="5">
         <v>14</v>
       </c>
@@ -9115,7 +9053,6 @@
       <c r="D114" s="5">
         <v>2</v>
       </c>
-      <c r="E114" s="5"/>
       <c r="F114" s="5">
         <v>14</v>
       </c>
@@ -9137,6 +9074,7 @@
       <c r="L114" s="5">
         <v>15</v>
       </c>
+      <c r="M114" s="22"/>
       <c r="N114" s="5" t="s">
         <v>194</v>
       </c>
@@ -9222,7 +9160,6 @@
       <c r="D116" s="5">
         <v>2</v>
       </c>
-      <c r="E116" s="5"/>
       <c r="F116" s="5">
         <v>14</v>
       </c>
@@ -9278,7 +9215,6 @@
       <c r="D117" s="5">
         <v>2</v>
       </c>
-      <c r="E117" s="5"/>
       <c r="F117" s="5">
         <v>14</v>
       </c>
@@ -9332,7 +9268,6 @@
       <c r="D118" s="5">
         <v>2</v>
       </c>
-      <c r="E118" s="5"/>
       <c r="F118" s="5">
         <v>14</v>
       </c>
@@ -9388,7 +9323,6 @@
       <c r="D119" s="5">
         <v>2</v>
       </c>
-      <c r="E119" s="5"/>
       <c r="F119" s="5">
         <v>14</v>
       </c>
@@ -9442,7 +9376,6 @@
       <c r="D120" s="5">
         <v>2</v>
       </c>
-      <c r="E120" s="5"/>
       <c r="F120" s="5">
         <v>14</v>
       </c>
@@ -9492,11 +9425,9 @@
       <c r="B121" s="5">
         <v>2025</v>
       </c>
-      <c r="C121" s="5"/>
       <c r="D121" s="5">
         <v>2</v>
       </c>
-      <c r="E121" s="5"/>
       <c r="F121" s="5">
         <v>15</v>
       </c>
@@ -9550,7 +9481,6 @@
       <c r="D122" s="5">
         <v>2</v>
       </c>
-      <c r="E122" s="5"/>
       <c r="F122" s="5">
         <v>15</v>
       </c>
@@ -9600,11 +9530,9 @@
       <c r="B123" s="5">
         <v>2025</v>
       </c>
-      <c r="C123" s="5"/>
       <c r="D123" s="5">
         <v>2</v>
       </c>
-      <c r="E123" s="5"/>
       <c r="F123" s="5">
         <v>15</v>
       </c>
@@ -9658,7 +9586,6 @@
       <c r="D124" s="5">
         <v>2</v>
       </c>
-      <c r="E124" s="5"/>
       <c r="F124" s="5">
         <v>15</v>
       </c>
@@ -9685,7 +9612,6 @@
       <c r="O124" s="5">
         <v>74330</v>
       </c>
-      <c r="P124" s="5"/>
       <c r="Q124" s="5" t="s">
         <v>237</v>
       </c>
@@ -9704,11 +9630,9 @@
       <c r="B125" s="5">
         <v>2025</v>
       </c>
-      <c r="C125" s="5"/>
       <c r="D125" s="5">
         <v>2</v>
       </c>
-      <c r="E125" s="5"/>
       <c r="F125" s="5">
         <v>16</v>
       </c>
@@ -9756,11 +9680,9 @@
       <c r="B126" s="5">
         <v>2025</v>
       </c>
-      <c r="C126" s="5"/>
       <c r="D126" s="5">
         <v>2</v>
       </c>
-      <c r="E126" s="5"/>
       <c r="F126" s="5">
         <v>16</v>
       </c>
@@ -9776,10 +9698,10 @@
       <c r="J126" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="K126" s="5"/>
       <c r="L126" s="5">
         <v>16</v>
       </c>
+      <c r="M126" s="22"/>
       <c r="N126" s="5" t="s">
         <v>25</v>
       </c>
@@ -9807,11 +9729,9 @@
       <c r="B127" s="5">
         <v>2025</v>
       </c>
-      <c r="C127" s="5"/>
       <c r="D127" s="5">
         <v>2</v>
       </c>
-      <c r="E127" s="5"/>
       <c r="F127" s="5">
         <v>16</v>
       </c>
@@ -9827,10 +9747,10 @@
       <c r="J127" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="K127" s="5"/>
       <c r="L127" s="5">
         <v>16</v>
       </c>
+      <c r="M127" s="22"/>
       <c r="N127" s="5" t="s">
         <v>25</v>
       </c>
@@ -9870,7 +9790,6 @@
       <c r="D128" s="5">
         <v>2</v>
       </c>
-      <c r="E128" s="5"/>
       <c r="F128" s="5">
         <v>16</v>
       </c>
@@ -9886,10 +9805,10 @@
       <c r="J128" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="K128" s="5"/>
       <c r="L128" s="5">
         <v>16</v>
       </c>
+      <c r="M128" s="22"/>
       <c r="N128" s="5" t="s">
         <v>25</v>
       </c>
@@ -9917,11 +9836,9 @@
       <c r="B129" s="5">
         <v>2025</v>
       </c>
-      <c r="C129" s="5"/>
       <c r="D129" s="5">
         <v>2</v>
       </c>
-      <c r="E129" s="5"/>
       <c r="F129" s="5">
         <v>16</v>
       </c>
@@ -9937,7 +9854,6 @@
       <c r="J129" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="K129" s="5"/>
       <c r="L129" s="5">
         <v>16</v>
       </c>
@@ -10023,11 +9939,9 @@
       <c r="B131" s="5">
         <v>2025</v>
       </c>
-      <c r="C131" s="5"/>
       <c r="D131" s="5">
         <v>2</v>
       </c>
-      <c r="E131" s="5"/>
       <c r="F131" s="5">
         <v>16</v>
       </c>
@@ -10043,7 +9957,6 @@
       <c r="J131" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="K131" s="5"/>
       <c r="L131" s="5">
         <v>17</v>
       </c>
@@ -10081,7 +9994,6 @@
       <c r="D132" s="5">
         <v>2</v>
       </c>
-      <c r="E132" s="5"/>
       <c r="F132" s="5">
         <v>16</v>
       </c>
@@ -10097,7 +10009,6 @@
       <c r="J132" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="K132" s="5"/>
       <c r="L132" s="5">
         <v>16</v>
       </c>
@@ -10123,11 +10034,9 @@
       <c r="B133" s="5">
         <v>2025</v>
       </c>
-      <c r="C133" s="5"/>
       <c r="D133" s="5">
         <v>2</v>
       </c>
-      <c r="E133" s="5"/>
       <c r="F133" s="5">
         <v>17</v>
       </c>
@@ -10143,7 +10052,6 @@
       <c r="J133" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="K133" s="5"/>
       <c r="L133" s="5">
         <v>17</v>
       </c>
@@ -10181,11 +10089,9 @@
       <c r="B134" s="5">
         <v>2025</v>
       </c>
-      <c r="C134" s="5"/>
       <c r="D134" s="5">
         <v>2</v>
       </c>
-      <c r="E134" s="5"/>
       <c r="F134" s="5">
         <v>17</v>
       </c>
@@ -10201,7 +10107,6 @@
       <c r="J134" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="K134" s="5"/>
       <c r="L134" s="5">
         <v>17</v>
       </c>
@@ -10239,11 +10144,9 @@
       <c r="B135" s="5">
         <v>2025</v>
       </c>
-      <c r="C135" s="5"/>
       <c r="D135" s="5">
         <v>2</v>
       </c>
-      <c r="E135" s="5"/>
       <c r="F135" s="5">
         <v>17</v>
       </c>
@@ -10259,7 +10162,6 @@
       <c r="J135" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="K135" s="5"/>
       <c r="L135" s="5">
         <v>17</v>
       </c>
@@ -10291,11 +10193,9 @@
       <c r="B136" s="5">
         <v>2025</v>
       </c>
-      <c r="C136" s="5"/>
       <c r="D136" s="5">
         <v>2</v>
       </c>
-      <c r="E136" s="5"/>
       <c r="F136" s="5">
         <v>17</v>
       </c>
@@ -10311,7 +10211,6 @@
       <c r="J136" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="K136" s="5"/>
       <c r="L136" s="5">
         <v>17</v>
       </c>
@@ -10320,7 +10219,6 @@
         <v>25</v>
       </c>
       <c r="O136" s="5"/>
-      <c r="P136" s="5"/>
       <c r="Q136" s="5" t="s">
         <v>260</v>
       </c>
@@ -10345,7 +10243,6 @@
       <c r="D137" s="5">
         <v>2</v>
       </c>
-      <c r="E137" s="5"/>
       <c r="F137" s="5">
         <v>17</v>
       </c>
@@ -10451,11 +10348,9 @@
       <c r="B139" s="5">
         <v>2025</v>
       </c>
-      <c r="C139" s="5"/>
       <c r="D139" s="5">
         <v>2</v>
       </c>
-      <c r="E139" s="5"/>
       <c r="F139" s="5">
         <v>17</v>
       </c>
@@ -10499,11 +10394,9 @@
       <c r="B140" s="5">
         <v>2025</v>
       </c>
-      <c r="C140" s="5"/>
       <c r="D140" s="5">
         <v>2</v>
       </c>
-      <c r="E140" s="5"/>
       <c r="F140" s="5">
         <v>19</v>
       </c>
@@ -10619,11 +10512,9 @@
       <c r="B142" s="5">
         <v>2025</v>
       </c>
-      <c r="C142" s="5"/>
       <c r="D142" s="5">
         <v>3</v>
       </c>
-      <c r="E142" s="5"/>
       <c r="F142" s="5">
         <v>19</v>
       </c>
@@ -10739,7 +10630,6 @@
       <c r="D144" s="5">
         <v>2</v>
       </c>
-      <c r="E144" s="5"/>
       <c r="F144" s="5">
         <v>19</v>
       </c>
@@ -10855,7 +10745,6 @@
       <c r="B146" s="5">
         <v>2025</v>
       </c>
-      <c r="C146" s="5"/>
       <c r="D146" s="5">
         <v>1</v>
       </c>
@@ -10917,7 +10806,6 @@
       <c r="B147" s="5">
         <v>2025</v>
       </c>
-      <c r="C147" s="5"/>
       <c r="D147" s="5">
         <v>1</v>
       </c>
@@ -10979,7 +10867,6 @@
       <c r="B148" s="5">
         <v>2025</v>
       </c>
-      <c r="C148" s="5"/>
       <c r="D148" s="5">
         <v>2</v>
       </c>
@@ -11233,7 +11120,6 @@
       <c r="B152" s="5">
         <v>2025</v>
       </c>
-      <c r="C152" s="5"/>
       <c r="D152" s="5">
         <v>2</v>
       </c>
@@ -11295,7 +11181,6 @@
       <c r="B153" s="5">
         <v>2025</v>
       </c>
-      <c r="C153" s="5"/>
       <c r="D153" s="5">
         <v>2</v>
       </c>
@@ -11356,7 +11241,6 @@
       <c r="B154" s="5">
         <v>2025</v>
       </c>
-      <c r="C154" s="5"/>
       <c r="D154" s="5">
         <v>2</v>
       </c>
@@ -11417,7 +11301,6 @@
       <c r="B155" s="5">
         <v>2025</v>
       </c>
-      <c r="C155" s="5"/>
       <c r="D155" s="5">
         <v>2</v>
       </c>
@@ -11452,7 +11335,6 @@
       <c r="O155" s="5">
         <v>96074</v>
       </c>
-      <c r="P155" s="5"/>
       <c r="Q155" s="5" t="s">
         <v>284</v>
       </c>
@@ -11479,7 +11361,6 @@
       <c r="B156" s="5">
         <v>2025</v>
       </c>
-      <c r="C156" s="5"/>
       <c r="D156" s="5">
         <v>2</v>
       </c>
@@ -11516,7 +11397,6 @@
       <c r="O156" s="5">
         <v>94643</v>
       </c>
-      <c r="P156" s="5"/>
       <c r="Q156" s="5" t="s">
         <v>284</v>
       </c>
@@ -11543,7 +11423,6 @@
       <c r="B157" s="5">
         <v>2025</v>
       </c>
-      <c r="C157" s="5"/>
       <c r="D157" s="5">
         <v>2</v>
       </c>
@@ -11660,14 +11539,13 @@
         <v>29</v>
       </c>
     </row>
-    <row r="159" spans="1:22">
-      <c r="A159" s="5">
+    <row r="159" spans="1:22" hidden="1">
+      <c r="A159" s="100">
         <v>158</v>
       </c>
       <c r="B159" s="5">
         <v>2026</v>
       </c>
-      <c r="C159" s="5"/>
       <c r="D159" s="5">
         <v>2</v>
       </c>
@@ -11708,7 +11586,7 @@
       <c r="Q159" s="5" t="s">
         <v>305</v>
       </c>
-      <c r="R159" s="5">
+      <c r="R159" s="22">
         <v>1</v>
       </c>
       <c r="S159" s="11" t="s">
@@ -11717,8 +11595,8 @@
       <c r="U159" s="5"/>
       <c r="V159" s="5"/>
     </row>
-    <row r="160" spans="1:22">
-      <c r="A160" s="9">
+    <row r="160" spans="1:22" hidden="1">
+      <c r="A160" s="101">
         <v>159</v>
       </c>
       <c r="B160" s="5">
@@ -11765,8 +11643,8 @@
         <v>311</v>
       </c>
     </row>
-    <row r="161" spans="1:37" ht="30">
-      <c r="A161" s="9">
+    <row r="161" spans="1:37" ht="30" hidden="1">
+      <c r="A161" s="101">
         <v>160</v>
       </c>
       <c r="B161" s="5">
@@ -11813,8 +11691,8 @@
         <v>233</v>
       </c>
     </row>
-    <row r="162" spans="1:37">
-      <c r="A162" s="5">
+    <row r="162" spans="1:37" hidden="1">
+      <c r="A162" s="102">
         <v>161</v>
       </c>
       <c r="B162" s="5">
@@ -11847,7 +11725,6 @@
       <c r="L162" s="5">
         <v>1</v>
       </c>
-      <c r="M162" s="5"/>
       <c r="N162" s="5" t="s">
         <v>25</v>
       </c>
@@ -11861,8 +11738,8 @@
         <v>305</v>
       </c>
     </row>
-    <row r="163" spans="1:37">
-      <c r="A163" s="9">
+    <row r="163" spans="1:37" hidden="1">
+      <c r="A163" s="100">
         <v>162</v>
       </c>
       <c r="B163" s="5">
@@ -11895,7 +11772,6 @@
       <c r="L163" s="5">
         <v>1</v>
       </c>
-      <c r="M163" s="5"/>
       <c r="N163" s="5" t="s">
         <v>25</v>
       </c>
@@ -11925,8 +11801,8 @@
       <c r="AI163" s="5"/>
       <c r="AK163" s="34"/>
     </row>
-    <row r="164" spans="1:37">
-      <c r="A164" s="9">
+    <row r="164" spans="1:37" hidden="1">
+      <c r="A164" s="100">
         <v>163</v>
       </c>
       <c r="B164" s="5">
@@ -11959,14 +11835,12 @@
       <c r="L164" s="5">
         <v>2</v>
       </c>
-      <c r="M164" s="5"/>
       <c r="N164" s="5" t="s">
         <v>25</v>
       </c>
       <c r="O164" s="5">
         <v>116755</v>
       </c>
-      <c r="P164" s="5"/>
       <c r="Q164" s="5" t="s">
         <v>316</v>
       </c>
@@ -11987,8 +11861,8 @@
       <c r="AI164" s="5"/>
       <c r="AK164" s="34"/>
     </row>
-    <row r="165" spans="1:37">
-      <c r="A165" s="5">
+    <row r="165" spans="1:37" hidden="1">
+      <c r="A165" s="100">
         <v>164</v>
       </c>
       <c r="B165" s="5">
@@ -12021,7 +11895,6 @@
       <c r="L165" s="5">
         <v>2</v>
       </c>
-      <c r="M165" s="5"/>
       <c r="N165" s="5" t="s">
         <v>25</v>
       </c>
@@ -12051,8 +11924,8 @@
       <c r="AI165" s="5"/>
       <c r="AK165" s="34"/>
     </row>
-    <row r="166" spans="1:37">
-      <c r="A166" s="9">
+    <row r="166" spans="1:37" hidden="1">
+      <c r="A166" s="100">
         <v>165</v>
       </c>
       <c r="B166" s="5">
@@ -12085,7 +11958,6 @@
       <c r="L166" s="5">
         <v>2</v>
       </c>
-      <c r="M166" s="5"/>
       <c r="N166" s="5" t="s">
         <v>25</v>
       </c>
@@ -12113,8 +11985,8 @@
       <c r="AI166" s="5"/>
       <c r="AK166" s="34"/>
     </row>
-    <row r="167" spans="1:37">
-      <c r="A167" s="9">
+    <row r="167" spans="1:37" hidden="1">
+      <c r="A167" s="100">
         <v>166</v>
       </c>
       <c r="B167" s="5">
@@ -12144,8 +12016,6 @@
       <c r="K167" s="5">
         <v>3</v>
       </c>
-      <c r="L167" s="5"/>
-      <c r="M167" s="5"/>
       <c r="N167" s="5" t="s">
         <v>25</v>
       </c>
@@ -12155,7 +12025,6 @@
       <c r="P167" s="5">
         <v>8533</v>
       </c>
-      <c r="Q167" s="5"/>
       <c r="S167" s="21"/>
       <c r="U167" s="5"/>
       <c r="W167" s="5"/>
@@ -12173,8 +12042,8 @@
       <c r="AI167" s="5"/>
       <c r="AK167" s="34"/>
     </row>
-    <row r="168" spans="1:37" ht="30">
-      <c r="A168" s="5">
+    <row r="168" spans="1:37" ht="30" hidden="1">
+      <c r="A168" s="100">
         <v>167</v>
       </c>
       <c r="B168" s="5">
@@ -12207,7 +12076,6 @@
       <c r="L168" s="5">
         <v>4</v>
       </c>
-      <c r="M168" s="5"/>
       <c r="N168" s="5" t="s">
         <v>25</v>
       </c>
@@ -12237,8 +12105,8 @@
       <c r="AI168" s="5"/>
       <c r="AK168" s="34"/>
     </row>
-    <row r="169" spans="1:37" ht="15.75">
-      <c r="A169" s="9">
+    <row r="169" spans="1:37" ht="15.75" hidden="1">
+      <c r="A169" s="100">
         <v>168</v>
       </c>
       <c r="B169" s="5">
@@ -12271,7 +12139,6 @@
       <c r="L169" s="5">
         <v>5</v>
       </c>
-      <c r="M169" s="5"/>
       <c r="N169" s="5" t="s">
         <v>25</v>
       </c>
@@ -12301,8 +12168,8 @@
       <c r="AI169" s="5"/>
       <c r="AK169" s="34"/>
     </row>
-    <row r="170" spans="1:37">
-      <c r="A170" s="9">
+    <row r="170" spans="1:37" hidden="1">
+      <c r="A170" s="100">
         <v>169</v>
       </c>
       <c r="B170" s="5">
@@ -12342,13 +12209,12 @@
       <c r="O170" s="5">
         <v>130671</v>
       </c>
-      <c r="P170" s="5"/>
       <c r="Q170" s="5" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="171" spans="1:37">
-      <c r="A171" s="5">
+    <row r="171" spans="1:37" hidden="1">
+      <c r="A171" s="100">
         <v>170</v>
       </c>
       <c r="B171" s="5">
@@ -12388,351 +12254,348 @@
       <c r="O171" s="5">
         <v>130691</v>
       </c>
-      <c r="P171" s="5"/>
       <c r="Q171" s="5" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="172" spans="1:37">
-      <c r="A172" s="9">
+    <row r="172" spans="1:37" hidden="1">
+      <c r="A172" s="100">
         <v>171</v>
       </c>
       <c r="B172" s="5">
         <v>2026</v>
       </c>
-      <c r="D172" s="82">
-        <v>2</v>
-      </c>
-      <c r="E172" s="82" t="s">
+      <c r="D172" s="5">
+        <v>2</v>
+      </c>
+      <c r="E172" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="F172" s="82">
+      <c r="F172" s="5">
         <v>4</v>
       </c>
-      <c r="G172" s="82" t="s">
-        <v>32</v>
-      </c>
-      <c r="H172" s="82" t="s">
-        <v>32</v>
-      </c>
-      <c r="I172" s="77" t="s">
+      <c r="G172" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H172" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I172" s="11" t="s">
         <v>328</v>
       </c>
-      <c r="J172" s="82" t="s">
+      <c r="J172" s="5" t="s">
         <v>277</v>
       </c>
-      <c r="K172" s="82">
+      <c r="K172" s="5">
         <v>4</v>
       </c>
-      <c r="L172" s="82">
+      <c r="L172" s="5">
         <v>5</v>
       </c>
       <c r="M172" s="21"/>
-      <c r="N172" s="82" t="s">
-        <v>25</v>
-      </c>
-      <c r="O172" s="82">
+      <c r="N172" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="O172" s="5">
         <v>130402</v>
       </c>
-      <c r="P172" s="82"/>
-      <c r="Q172" s="82" t="s">
+      <c r="Q172" s="5" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="173" spans="1:37">
-      <c r="A173" s="9">
+    <row r="173" spans="1:37" hidden="1">
+      <c r="A173" s="100">
         <v>172</v>
       </c>
       <c r="B173" s="5">
         <v>2026</v>
       </c>
-      <c r="D173" s="50">
-        <v>2</v>
-      </c>
-      <c r="E173" s="50" t="s">
+      <c r="D173" s="5">
+        <v>2</v>
+      </c>
+      <c r="E173" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="F173" s="50">
+      <c r="F173" s="5">
         <v>5</v>
       </c>
-      <c r="G173" s="50" t="s">
-        <v>32</v>
-      </c>
-      <c r="H173" s="50" t="s">
-        <v>32</v>
-      </c>
-      <c r="I173" s="85" t="s">
+      <c r="G173" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H173" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I173" s="11" t="s">
         <v>329</v>
       </c>
-      <c r="J173" s="50" t="s">
+      <c r="J173" s="5" t="s">
         <v>277</v>
       </c>
-      <c r="K173" s="50">
+      <c r="K173" s="5">
         <v>5</v>
       </c>
-      <c r="L173" s="50">
+      <c r="L173" s="5">
         <v>5</v>
       </c>
       <c r="M173" s="21"/>
-      <c r="N173" s="50" t="s">
-        <v>25</v>
-      </c>
-      <c r="O173" s="50">
+      <c r="N173" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="O173" s="5">
         <v>133267</v>
       </c>
-      <c r="P173" s="86" t="s">
+      <c r="P173" s="95" t="s">
         <v>330</v>
       </c>
-      <c r="Q173" s="50" t="s">
+      <c r="Q173" s="5" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="174" spans="1:37">
-      <c r="A174" s="5">
+    <row r="174" spans="1:37" hidden="1">
+      <c r="A174" s="100">
         <v>173</v>
       </c>
       <c r="B174" s="5">
         <v>2026</v>
       </c>
-      <c r="D174" s="50">
-        <v>2</v>
-      </c>
-      <c r="E174" s="50" t="s">
+      <c r="D174" s="5">
+        <v>2</v>
+      </c>
+      <c r="E174" s="5" t="s">
         <v>281</v>
       </c>
-      <c r="F174" s="50">
+      <c r="F174" s="5">
         <v>6</v>
       </c>
-      <c r="G174" s="50" t="s">
+      <c r="G174" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="H174" s="50" t="s">
+      <c r="H174" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="I174" s="85" t="s">
+      <c r="I174" s="11" t="s">
         <v>332</v>
       </c>
-      <c r="J174" s="50" t="s">
+      <c r="J174" s="5" t="s">
         <v>277</v>
       </c>
-      <c r="K174" s="50">
+      <c r="K174" s="5">
         <v>6</v>
       </c>
-      <c r="L174" s="50">
+      <c r="L174" s="5">
         <v>6</v>
       </c>
       <c r="M174" s="21"/>
-      <c r="N174" s="50" t="s">
-        <v>25</v>
-      </c>
-      <c r="O174" s="92">
+      <c r="N174" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="O174" s="96">
         <v>138671</v>
       </c>
-      <c r="P174" s="90">
+      <c r="P174" s="95">
         <v>51051</v>
       </c>
-      <c r="Q174" s="50" t="s">
+      <c r="Q174" s="5" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="175" spans="1:37">
-      <c r="A175" s="9">
+    <row r="175" spans="1:37" hidden="1">
+      <c r="A175" s="100">
         <v>174</v>
       </c>
       <c r="B175" s="5">
         <v>2026</v>
       </c>
-      <c r="D175" s="87">
-        <v>2</v>
-      </c>
-      <c r="E175" s="87" t="s">
+      <c r="D175" s="5">
+        <v>2</v>
+      </c>
+      <c r="E175" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="F175" s="87">
+      <c r="F175" s="5">
         <v>5</v>
       </c>
-      <c r="G175" s="87" t="s">
-        <v>32</v>
-      </c>
-      <c r="H175" s="87" t="s">
-        <v>32</v>
-      </c>
-      <c r="I175" s="88" t="s">
+      <c r="G175" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H175" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I175" s="11" t="s">
         <v>333</v>
       </c>
-      <c r="J175" s="87" t="s">
+      <c r="J175" s="5" t="s">
         <v>334</v>
       </c>
-      <c r="K175" s="87">
+      <c r="K175" s="5">
         <v>5</v>
       </c>
-      <c r="L175" s="87">
+      <c r="L175" s="5">
         <v>6</v>
       </c>
       <c r="M175" s="21"/>
-      <c r="N175" s="87" t="s">
-        <v>25</v>
-      </c>
-      <c r="O175" s="93">
+      <c r="N175" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="O175" s="96">
         <v>133978</v>
       </c>
-      <c r="P175" s="86" t="s">
+      <c r="P175" s="95" t="s">
         <v>335</v>
       </c>
-      <c r="Q175" s="89" t="s">
+      <c r="Q175" s="5" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="176" spans="1:37">
-      <c r="A176" s="9">
+    <row r="176" spans="1:37" hidden="1">
+      <c r="A176" s="100">
         <v>175</v>
       </c>
       <c r="B176" s="5">
         <v>2026</v>
       </c>
-      <c r="D176" s="87">
-        <v>2</v>
-      </c>
-      <c r="E176" s="87" t="s">
+      <c r="D176" s="5">
+        <v>2</v>
+      </c>
+      <c r="E176" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="F176" s="87">
+      <c r="F176" s="5">
         <v>6</v>
       </c>
-      <c r="G176" s="87" t="s">
+      <c r="G176" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="H176" s="87" t="s">
+      <c r="H176" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="I176" s="88" t="s">
+      <c r="I176" s="11" t="s">
         <v>337</v>
       </c>
-      <c r="J176" s="87" t="s">
+      <c r="J176" s="5" t="s">
         <v>334</v>
       </c>
-      <c r="K176" s="87">
+      <c r="K176" s="5">
         <v>6</v>
       </c>
-      <c r="L176" s="87">
+      <c r="L176" s="5">
         <v>7</v>
       </c>
       <c r="M176" s="21"/>
-      <c r="N176" s="87" t="s">
-        <v>25</v>
-      </c>
-      <c r="O176" s="93">
+      <c r="N176" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="O176" s="96">
         <v>140033</v>
       </c>
-      <c r="P176" s="86" t="s">
+      <c r="P176" s="95" t="s">
         <v>338</v>
       </c>
-      <c r="Q176" s="89" t="s">
+      <c r="Q176" s="5" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="177" spans="1:31">
-      <c r="A177" s="5">
+    <row r="177" spans="1:47" hidden="1">
+      <c r="A177" s="100">
         <v>176</v>
       </c>
       <c r="B177" s="5">
         <v>2026</v>
       </c>
-      <c r="D177" s="87">
-        <v>2</v>
-      </c>
-      <c r="E177" s="87" t="s">
+      <c r="D177" s="5">
+        <v>2</v>
+      </c>
+      <c r="E177" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="F177" s="87">
+      <c r="F177" s="5">
         <v>6</v>
       </c>
-      <c r="G177" s="87" t="s">
+      <c r="G177" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="H177" s="87" t="s">
+      <c r="H177" s="5" t="s">
         <v>339</v>
       </c>
-      <c r="I177" s="88" t="s">
+      <c r="I177" s="11" t="s">
         <v>340</v>
       </c>
-      <c r="J177" s="87" t="s">
+      <c r="J177" s="5" t="s">
         <v>334</v>
       </c>
-      <c r="K177" s="87">
+      <c r="K177" s="5">
         <v>6</v>
       </c>
-      <c r="L177" s="87">
+      <c r="L177" s="5">
         <v>7</v>
       </c>
       <c r="M177" s="21"/>
-      <c r="N177" s="87" t="s">
-        <v>25</v>
-      </c>
-      <c r="O177" s="93">
+      <c r="N177" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="O177" s="96">
         <v>142693</v>
       </c>
-      <c r="P177" s="86"/>
-      <c r="Q177" s="89" t="s">
+      <c r="P177" s="95"/>
+      <c r="Q177" s="5" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="178" spans="1:31" ht="30">
-      <c r="A178" s="9">
+    <row r="178" spans="1:47" ht="30" hidden="1">
+      <c r="A178" s="100">
         <v>177</v>
       </c>
-      <c r="B178" s="82">
+      <c r="B178" s="5">
         <v>2026</v>
       </c>
-      <c r="D178" s="95">
-        <v>2</v>
-      </c>
-      <c r="E178" s="95" t="s">
+      <c r="D178" s="5">
+        <v>2</v>
+      </c>
+      <c r="E178" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="F178" s="95">
+      <c r="F178" s="5">
         <v>6</v>
       </c>
-      <c r="G178" s="95" t="s">
+      <c r="G178" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="H178" s="95" t="s">
+      <c r="H178" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="I178" s="96" t="s">
+      <c r="I178" s="11" t="s">
         <v>341</v>
       </c>
-      <c r="J178" s="95" t="s">
+      <c r="J178" s="5" t="s">
         <v>334</v>
       </c>
-      <c r="K178" s="95">
+      <c r="K178" s="5">
         <v>6</v>
       </c>
-      <c r="L178" s="95">
+      <c r="L178" s="5">
         <v>7</v>
       </c>
       <c r="M178" s="21"/>
-      <c r="N178" s="95" t="s">
-        <v>25</v>
-      </c>
-      <c r="O178" s="97">
+      <c r="N178" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="O178" s="96">
         <v>142692</v>
       </c>
-      <c r="P178" s="98">
+      <c r="P178" s="95">
         <v>62489</v>
       </c>
-      <c r="Q178" s="99" t="s">
+      <c r="Q178" s="5" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="179" spans="1:31" ht="16.5">
-      <c r="A179" s="9">
+    <row r="179" spans="1:47" hidden="1">
+      <c r="A179" s="100">
         <v>178</v>
       </c>
       <c r="B179" s="5">
         <v>2026</v>
       </c>
-      <c r="C179" s="5"/>
       <c r="D179" s="5">
         <v>2</v>
       </c>
@@ -12764,24 +12627,23 @@
       <c r="N179" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="O179" s="100">
+      <c r="O179" s="92">
         <v>133866</v>
       </c>
-      <c r="P179" s="101">
+      <c r="P179" s="92">
         <v>40881</v>
       </c>
       <c r="Q179" s="5" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="180" spans="1:31">
-      <c r="A180" s="5">
+    <row r="180" spans="1:47" hidden="1">
+      <c r="A180" s="100">
         <v>179</v>
       </c>
       <c r="B180" s="5">
         <v>2026</v>
       </c>
-      <c r="C180" s="5"/>
       <c r="D180" s="5">
         <v>2</v>
       </c>
@@ -12809,12 +12671,14 @@
       <c r="L180" s="5">
         <v>8</v>
       </c>
-      <c r="M180" s="89"/>
+      <c r="M180" s="103"/>
       <c r="N180" s="5" t="s">
-        <v>365</v>
-      </c>
-      <c r="O180" s="5"/>
-      <c r="P180" s="105">
+        <v>303</v>
+      </c>
+      <c r="O180" s="92">
+        <v>145211</v>
+      </c>
+      <c r="P180" s="92">
         <v>64229</v>
       </c>
       <c r="Q180" s="5" t="s">
@@ -12830,18 +12694,17 @@
       <c r="Z180" s="87"/>
       <c r="AA180" s="87"/>
       <c r="AB180" s="87"/>
-      <c r="AC180" s="93"/>
+      <c r="AC180" s="91"/>
       <c r="AD180" s="86"/>
       <c r="AE180" s="89"/>
     </row>
-    <row r="181" spans="1:31" ht="30">
-      <c r="A181" s="9">
+    <row r="181" spans="1:47" ht="30" hidden="1">
+      <c r="A181" s="100">
         <v>180</v>
       </c>
       <c r="B181" s="5">
         <v>2026</v>
       </c>
-      <c r="C181" s="5"/>
       <c r="D181" s="5">
         <v>2</v>
       </c>
@@ -12870,26 +12733,25 @@
         <v>8</v>
       </c>
       <c r="N181" s="5" t="s">
-        <v>347</v>
-      </c>
-      <c r="O181" s="102">
+        <v>25</v>
+      </c>
+      <c r="O181" s="92">
         <v>144762</v>
       </c>
-      <c r="P181" s="103">
+      <c r="P181" s="92">
         <v>64032</v>
       </c>
       <c r="Q181" s="5" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="182" spans="1:31">
-      <c r="A182" s="9">
+    <row r="182" spans="1:47" hidden="1">
+      <c r="A182" s="100">
         <v>181</v>
       </c>
       <c r="B182" s="5">
         <v>2026</v>
       </c>
-      <c r="C182" s="5"/>
       <c r="D182" s="5">
         <v>2</v>
       </c>
@@ -12906,7 +12768,7 @@
         <v>258</v>
       </c>
       <c r="I182" s="11" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="J182" s="5" t="s">
         <v>24</v>
@@ -12919,24 +12781,23 @@
       </c>
       <c r="M182" s="21"/>
       <c r="N182" s="5" t="s">
-        <v>347</v>
-      </c>
-      <c r="O182" s="104">
+        <v>25</v>
+      </c>
+      <c r="O182" s="92">
         <v>144725</v>
       </c>
-      <c r="P182" s="5"/>
+      <c r="P182" s="92"/>
       <c r="Q182" s="5" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="183" spans="1:31" ht="15.75">
-      <c r="A183" s="5">
+    <row r="183" spans="1:47" hidden="1">
+      <c r="A183" s="100">
         <v>182</v>
       </c>
       <c r="B183" s="5">
         <v>2026</v>
       </c>
-      <c r="C183" s="5"/>
       <c r="D183" s="5">
         <v>2</v>
       </c>
@@ -12953,7 +12814,7 @@
         <v>41</v>
       </c>
       <c r="I183" s="11" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="J183" s="5" t="s">
         <v>277</v>
@@ -12965,598 +12826,1340 @@
         <v>8</v>
       </c>
       <c r="N183" s="5" t="s">
-        <v>347</v>
-      </c>
-      <c r="O183" s="102">
+        <v>25</v>
+      </c>
+      <c r="O183" s="92">
         <v>145189</v>
       </c>
-      <c r="P183" s="103">
+      <c r="P183" s="92">
         <v>64674</v>
       </c>
       <c r="Q183" s="5" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="184" spans="1:31">
-      <c r="A184" s="9">
+    <row r="184" spans="1:47" hidden="1">
+      <c r="A184" s="100">
         <v>183</v>
       </c>
-      <c r="B184" s="82">
+      <c r="B184" s="5">
         <v>2026</v>
       </c>
-      <c r="C184" s="82"/>
-      <c r="D184" s="82">
-        <v>2</v>
-      </c>
-      <c r="E184" s="82" t="s">
+      <c r="D184" s="5">
+        <v>2</v>
+      </c>
+      <c r="E184" s="5" t="s">
         <v>281</v>
       </c>
-      <c r="F184" s="82">
+      <c r="F184" s="5">
         <v>8</v>
       </c>
-      <c r="G184" s="82" t="s">
+      <c r="G184" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="H184" s="82" t="s">
+      <c r="H184" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="I184" s="77" t="s">
+      <c r="I184" s="11" t="s">
+        <v>349</v>
+      </c>
+      <c r="J184" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="K184" s="5">
+        <v>8</v>
+      </c>
+      <c r="L184" s="5">
+        <v>8</v>
+      </c>
+      <c r="M184" s="78"/>
+      <c r="N184" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="O184" s="92">
+        <v>147174</v>
+      </c>
+      <c r="P184" s="92">
+        <v>70214</v>
+      </c>
+      <c r="Q184" s="5" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="185" spans="1:47" hidden="1">
+      <c r="A185" s="100">
+        <v>184</v>
+      </c>
+      <c r="B185" s="5">
+        <v>2026</v>
+      </c>
+      <c r="D185" s="5">
+        <v>2</v>
+      </c>
+      <c r="E185" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="F185" s="5">
+        <v>8</v>
+      </c>
+      <c r="G185" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H185" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I185" s="11" t="s">
         <v>350</v>
       </c>
-      <c r="J184" s="82" t="s">
+      <c r="J185" s="5" t="s">
         <v>277</v>
       </c>
-      <c r="K184" s="82">
+      <c r="K185" s="5">
         <v>8</v>
       </c>
-      <c r="L184" s="82">
+      <c r="L185" s="5">
+        <v>9</v>
+      </c>
+      <c r="M185" s="78"/>
+      <c r="N185" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="O185" s="92">
+        <v>148757</v>
+      </c>
+      <c r="P185" s="92">
+        <v>69645</v>
+      </c>
+      <c r="Q185" s="92" t="s">
+        <v>233</v>
+      </c>
+      <c r="R185" s="92"/>
+    </row>
+    <row r="186" spans="1:47" hidden="1">
+      <c r="A186" s="100">
+        <v>185</v>
+      </c>
+      <c r="B186" s="5">
+        <v>2026</v>
+      </c>
+      <c r="D186" s="5">
+        <v>2</v>
+      </c>
+      <c r="E186" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="F186" s="5">
         <v>8</v>
       </c>
-      <c r="M184" s="26"/>
-      <c r="N184" s="82" t="s">
-        <v>347</v>
-      </c>
-      <c r="O184" s="106">
-        <v>147174</v>
-      </c>
-      <c r="P184" s="110">
-        <v>70214</v>
-      </c>
-      <c r="Q184" s="82" t="s">
+      <c r="G186" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="H186" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="I186" s="11" t="s">
+        <v>351</v>
+      </c>
+      <c r="J186" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="K186" s="5">
+        <v>8</v>
+      </c>
+      <c r="L186" s="5">
+        <v>9</v>
+      </c>
+      <c r="M186" s="104"/>
+      <c r="N186" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="O186" s="92">
+        <v>148758</v>
+      </c>
+      <c r="P186" s="92">
+        <v>69870</v>
+      </c>
+      <c r="Q186" s="92" t="s">
+        <v>197</v>
+      </c>
+      <c r="R186" s="92"/>
+    </row>
+    <row r="187" spans="1:47" hidden="1">
+      <c r="A187" s="100">
+        <v>186</v>
+      </c>
+      <c r="B187" s="5">
+        <v>2026</v>
+      </c>
+      <c r="D187" s="5">
+        <v>2</v>
+      </c>
+      <c r="E187" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="F187" s="5">
+        <v>8</v>
+      </c>
+      <c r="G187" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H187" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I187" s="11" t="s">
+        <v>353</v>
+      </c>
+      <c r="J187" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="K187" s="5">
+        <v>8</v>
+      </c>
+      <c r="L187" s="5">
+        <v>8</v>
+      </c>
+      <c r="M187" s="104"/>
+      <c r="N187" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="O187" s="92">
+        <v>148761</v>
+      </c>
+      <c r="P187" s="92">
+        <v>70249</v>
+      </c>
+      <c r="Q187" s="92" t="s">
+        <v>242</v>
+      </c>
+      <c r="R187" s="92"/>
+      <c r="S187" s="21"/>
+      <c r="AD187" s="5"/>
+      <c r="AE187" s="50"/>
+      <c r="AF187" s="50"/>
+      <c r="AG187" s="50"/>
+      <c r="AH187" s="50"/>
+      <c r="AI187" s="50"/>
+      <c r="AJ187" s="50"/>
+      <c r="AK187" s="50"/>
+      <c r="AL187" s="85"/>
+      <c r="AM187" s="50"/>
+      <c r="AN187" s="50"/>
+      <c r="AO187" s="50"/>
+      <c r="AP187" s="50"/>
+      <c r="AQ187" s="93"/>
+      <c r="AR187" s="94"/>
+      <c r="AS187" s="50"/>
+      <c r="AU187" s="34"/>
+    </row>
+    <row r="188" spans="1:47" hidden="1">
+      <c r="A188" s="100">
+        <v>187</v>
+      </c>
+      <c r="B188" s="5">
+        <v>2026</v>
+      </c>
+      <c r="D188" s="5">
+        <v>2</v>
+      </c>
+      <c r="E188" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="F188" s="5">
+        <v>8</v>
+      </c>
+      <c r="G188" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H188" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="I188" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="J188" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="K188" s="5">
+        <v>8</v>
+      </c>
+      <c r="L188" s="5">
+        <v>9</v>
+      </c>
+      <c r="M188" s="21"/>
+      <c r="N188" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="O188" s="92">
+        <v>148892</v>
+      </c>
+      <c r="P188" s="92" t="s">
+        <v>355</v>
+      </c>
+      <c r="Q188" s="92" t="s">
+        <v>205</v>
+      </c>
+      <c r="R188" s="92"/>
+    </row>
+    <row r="189" spans="1:47" hidden="1">
+      <c r="A189" s="100">
+        <v>188</v>
+      </c>
+      <c r="B189" s="5">
+        <v>2026</v>
+      </c>
+      <c r="D189" s="5">
+        <v>2</v>
+      </c>
+      <c r="E189" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="F189" s="5">
+        <v>8</v>
+      </c>
+      <c r="G189" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="H189" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="I189" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="J189" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="K189" s="5">
+        <v>9</v>
+      </c>
+      <c r="L189" s="5">
+        <v>9</v>
+      </c>
+      <c r="M189" s="21"/>
+      <c r="N189" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="O189" s="92">
+        <v>150032</v>
+      </c>
+      <c r="P189" s="92"/>
+      <c r="Q189" s="92" t="s">
+        <v>357</v>
+      </c>
+      <c r="R189" s="92"/>
+    </row>
+    <row r="190" spans="1:47" ht="30" hidden="1">
+      <c r="A190" s="100">
+        <v>189</v>
+      </c>
+      <c r="B190" s="5">
+        <v>2026</v>
+      </c>
+      <c r="D190" s="5">
+        <v>2</v>
+      </c>
+      <c r="E190" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="F190" s="5">
+        <v>8</v>
+      </c>
+      <c r="G190" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H190" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I190" s="11" t="s">
+        <v>358</v>
+      </c>
+      <c r="J190" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="K190" s="5">
+        <v>8</v>
+      </c>
+      <c r="L190" s="5">
+        <v>8</v>
+      </c>
+      <c r="M190" s="21"/>
+      <c r="N190" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="O190" s="92">
+        <v>149743</v>
+      </c>
+      <c r="P190" s="92">
+        <v>72476</v>
+      </c>
+      <c r="Q190" s="92" t="s">
+        <v>242</v>
+      </c>
+      <c r="R190" s="92"/>
+    </row>
+    <row r="191" spans="1:47" ht="30" hidden="1">
+      <c r="A191" s="100">
+        <v>190</v>
+      </c>
+      <c r="B191" s="5">
+        <v>2026</v>
+      </c>
+      <c r="D191" s="5">
+        <v>2</v>
+      </c>
+      <c r="E191" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="F191" s="5">
+        <v>9</v>
+      </c>
+      <c r="G191" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H191" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I191" s="11" t="s">
+        <v>359</v>
+      </c>
+      <c r="J191" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="K191" s="5">
+        <v>9</v>
+      </c>
+      <c r="L191" s="5">
+        <v>9</v>
+      </c>
+      <c r="N191" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="O191" s="92">
+        <v>151518</v>
+      </c>
+      <c r="P191" s="92" t="s">
+        <v>360</v>
+      </c>
+      <c r="Q191" s="92" t="s">
+        <v>229</v>
+      </c>
+      <c r="R191" s="92"/>
+    </row>
+    <row r="192" spans="1:47" hidden="1">
+      <c r="A192" s="100">
+        <v>191</v>
+      </c>
+      <c r="B192" s="5">
+        <v>2026</v>
+      </c>
+      <c r="D192" s="5">
+        <v>2</v>
+      </c>
+      <c r="E192" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="F192" s="5">
+        <v>9</v>
+      </c>
+      <c r="G192" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H192" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I192" s="11" t="s">
+        <v>361</v>
+      </c>
+      <c r="J192" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="K192" s="5">
+        <v>9</v>
+      </c>
+      <c r="L192" s="5">
+        <v>9</v>
+      </c>
+      <c r="N192" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="O192" s="92">
+        <v>151821</v>
+      </c>
+      <c r="P192" s="92">
+        <v>78292</v>
+      </c>
+      <c r="Q192" s="92" t="s">
+        <v>229</v>
+      </c>
+      <c r="R192" s="92"/>
+    </row>
+    <row r="193" spans="1:18" hidden="1">
+      <c r="A193" s="100">
+        <v>192</v>
+      </c>
+      <c r="B193" s="5">
+        <v>2026</v>
+      </c>
+      <c r="D193" s="5">
+        <v>2</v>
+      </c>
+      <c r="E193" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="F193" s="5">
+        <v>9</v>
+      </c>
+      <c r="G193" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H193" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I193" s="11" t="s">
+        <v>362</v>
+      </c>
+      <c r="J193" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="K193" s="5">
+        <v>9</v>
+      </c>
+      <c r="L193" s="5">
+        <v>9</v>
+      </c>
+      <c r="N193" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="O193" s="92">
+        <v>151822</v>
+      </c>
+      <c r="P193" s="92">
+        <v>78293</v>
+      </c>
+      <c r="Q193" s="92" t="s">
+        <v>331</v>
+      </c>
+      <c r="R193" s="92"/>
+    </row>
+    <row r="194" spans="1:18" hidden="1">
+      <c r="A194" s="100">
+        <v>193</v>
+      </c>
+      <c r="B194" s="5">
+        <v>2026</v>
+      </c>
+      <c r="D194" s="5">
+        <v>2</v>
+      </c>
+      <c r="E194" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="F194" s="5">
+        <v>9</v>
+      </c>
+      <c r="G194" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="H194" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="I194" s="11" t="s">
+        <v>363</v>
+      </c>
+      <c r="J194" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="K194" s="5">
+        <v>9</v>
+      </c>
+      <c r="L194" s="5">
+        <v>10</v>
+      </c>
+      <c r="N194" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="O194" s="92">
+        <v>152823</v>
+      </c>
+      <c r="P194" s="92">
+        <v>80198</v>
+      </c>
+      <c r="Q194" s="92" t="s">
         <v>235</v>
       </c>
-    </row>
-    <row r="185" spans="1:31" ht="15.75">
-      <c r="A185" s="9">
-        <v>184</v>
-      </c>
-      <c r="B185" s="82">
+      <c r="R194" s="92" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="195" spans="1:18">
+      <c r="A195" s="100">
+        <v>194</v>
+      </c>
+      <c r="B195" s="5">
         <v>2026</v>
       </c>
-      <c r="C185" s="82"/>
-      <c r="D185" s="82">
-        <v>2</v>
-      </c>
-      <c r="E185" s="82" t="s">
-        <v>212</v>
-      </c>
-      <c r="F185" s="82">
+      <c r="D195" s="5">
+        <v>2</v>
+      </c>
+      <c r="E195" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="F195" s="5">
+        <v>9</v>
+      </c>
+      <c r="G195" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="H195" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="I195" s="11" t="s">
+        <v>364</v>
+      </c>
+      <c r="J195" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="K195" s="5">
+        <v>9</v>
+      </c>
+      <c r="L195" s="5">
+        <v>10</v>
+      </c>
+      <c r="M195" s="33" t="s">
+        <v>352</v>
+      </c>
+      <c r="N195" s="5" t="s">
+        <v>352</v>
+      </c>
+      <c r="O195" s="92">
+        <v>152856</v>
+      </c>
+      <c r="P195" s="92">
+        <v>80398</v>
+      </c>
+      <c r="Q195" s="92" t="s">
+        <v>345</v>
+      </c>
+      <c r="R195" s="92" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="196" spans="1:18" ht="30" hidden="1">
+      <c r="A196" s="100">
+        <v>195</v>
+      </c>
+      <c r="B196" s="5">
+        <v>2026</v>
+      </c>
+      <c r="D196" s="5">
+        <v>1</v>
+      </c>
+      <c r="E196" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="F196" s="5">
+        <v>9</v>
+      </c>
+      <c r="G196" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="H196" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="I196" s="11" t="s">
+        <v>365</v>
+      </c>
+      <c r="J196" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="K196" s="5">
+        <v>9</v>
+      </c>
+      <c r="L196" s="5">
+        <v>9</v>
+      </c>
+      <c r="N196" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="O196" s="92">
+        <v>152929</v>
+      </c>
+      <c r="P196" s="92">
+        <v>80793</v>
+      </c>
+      <c r="Q196" s="92" t="s">
+        <v>366</v>
+      </c>
+      <c r="R196" s="92" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="197" spans="1:18" hidden="1">
+      <c r="A197" s="100">
+        <v>196</v>
+      </c>
+      <c r="B197" s="5">
+        <v>2026</v>
+      </c>
+      <c r="D197" s="5">
+        <v>2</v>
+      </c>
+      <c r="E197" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="F197" s="5">
+        <v>9</v>
+      </c>
+      <c r="G197" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="H197" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="I197" s="11" t="s">
+        <v>367</v>
+      </c>
+      <c r="J197" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="K197" s="5">
+        <v>9</v>
+      </c>
+      <c r="L197" s="5">
+        <v>9</v>
+      </c>
+      <c r="N197" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="O197" s="92">
+        <v>153032</v>
+      </c>
+      <c r="P197" s="92">
+        <v>81178</v>
+      </c>
+      <c r="Q197" s="92" t="s">
+        <v>357</v>
+      </c>
+      <c r="R197" s="92" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="198" spans="1:18" hidden="1">
+      <c r="A198" s="100">
+        <v>197</v>
+      </c>
+      <c r="B198" s="5">
+        <v>2026</v>
+      </c>
+      <c r="D198" s="5">
+        <v>2</v>
+      </c>
+      <c r="E198" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="F198" s="5">
+        <v>9</v>
+      </c>
+      <c r="G198" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H198" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="I198" s="11" t="s">
+        <v>369</v>
+      </c>
+      <c r="J198" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="K198" s="5">
+        <v>9</v>
+      </c>
+      <c r="L198" s="5">
+        <v>9</v>
+      </c>
+      <c r="M198" s="21"/>
+      <c r="N198" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="O198" s="92">
+        <v>153037</v>
+      </c>
+      <c r="P198" s="92"/>
+      <c r="Q198" s="92" t="s">
+        <v>370</v>
+      </c>
+      <c r="R198" s="92" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="199" spans="1:18" ht="30">
+      <c r="A199" s="100">
+        <v>198</v>
+      </c>
+      <c r="B199" s="5">
+        <v>2026</v>
+      </c>
+      <c r="D199" s="5">
+        <v>1</v>
+      </c>
+      <c r="E199" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="F199" s="5">
+        <v>9</v>
+      </c>
+      <c r="G199" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="H199" s="11" t="s">
+        <v>371</v>
+      </c>
+      <c r="I199" s="11" t="s">
+        <v>372</v>
+      </c>
+      <c r="J199" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="K199" s="5">
+        <v>9</v>
+      </c>
+      <c r="L199" s="5">
+        <v>10</v>
+      </c>
+      <c r="M199" s="21"/>
+      <c r="N199" s="5" t="s">
+        <v>352</v>
+      </c>
+      <c r="O199" s="92">
+        <v>153647</v>
+      </c>
+      <c r="P199" s="92">
+        <v>84266</v>
+      </c>
+      <c r="Q199" s="92" t="s">
+        <v>373</v>
+      </c>
+      <c r="R199" s="92"/>
+    </row>
+    <row r="200" spans="1:18" hidden="1">
+      <c r="A200" s="100">
+        <v>199</v>
+      </c>
+      <c r="B200" s="5">
+        <v>2026</v>
+      </c>
+      <c r="D200" s="5">
+        <v>2</v>
+      </c>
+      <c r="E200" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="F200" s="5">
+        <v>9</v>
+      </c>
+      <c r="G200" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H200" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I200" s="11" t="s">
+        <v>374</v>
+      </c>
+      <c r="J200" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="K200" s="5">
         <v>8</v>
       </c>
-      <c r="G185" s="82" t="s">
-        <v>32</v>
-      </c>
-      <c r="H185" s="82" t="s">
-        <v>32</v>
-      </c>
-      <c r="I185" s="77" t="s">
-        <v>351</v>
-      </c>
-      <c r="J185" s="82" t="s">
-        <v>334</v>
-      </c>
-      <c r="K185" s="82">
-        <v>8</v>
-      </c>
-      <c r="L185" s="82">
+      <c r="L200" s="5">
         <v>9</v>
       </c>
-      <c r="M185" s="26"/>
-      <c r="N185" s="82" t="s">
-        <v>347</v>
-      </c>
-      <c r="O185" s="106">
-        <v>148757</v>
-      </c>
-      <c r="P185" s="107">
-        <v>69645</v>
-      </c>
-      <c r="Q185" s="82" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="186" spans="1:31">
-      <c r="A186" s="5">
-        <v>185</v>
-      </c>
-      <c r="B186" s="50">
+      <c r="M200" s="21"/>
+      <c r="N200" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="O200" s="92">
+        <v>147124</v>
+      </c>
+      <c r="P200" s="92">
+        <v>66884</v>
+      </c>
+      <c r="Q200" s="92"/>
+      <c r="R200" s="92"/>
+    </row>
+    <row r="201" spans="1:18" ht="30">
+      <c r="A201" s="100">
+        <v>200</v>
+      </c>
+      <c r="B201" s="5">
         <v>2026</v>
       </c>
-      <c r="C186" s="50"/>
-      <c r="D186" s="50">
-        <v>2</v>
-      </c>
-      <c r="E186" s="50" t="s">
-        <v>212</v>
-      </c>
-      <c r="F186" s="50">
-        <v>8</v>
-      </c>
-      <c r="G186" s="50" t="s">
-        <v>41</v>
-      </c>
-      <c r="H186" s="50" t="s">
-        <v>41</v>
-      </c>
-      <c r="I186" s="85" t="s">
+      <c r="D201" s="5">
+        <v>2</v>
+      </c>
+      <c r="E201" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="F201" s="5">
+        <v>9</v>
+      </c>
+      <c r="G201" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="H201" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="I201" s="11" t="s">
+        <v>375</v>
+      </c>
+      <c r="J201" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="K201" s="5">
+        <v>9</v>
+      </c>
+      <c r="L201" s="5">
+        <v>10</v>
+      </c>
+      <c r="M201" s="21"/>
+      <c r="N201" s="5" t="s">
         <v>352</v>
       </c>
-      <c r="J186" s="50" t="s">
-        <v>334</v>
-      </c>
-      <c r="K186" s="50">
-        <v>8</v>
-      </c>
-      <c r="L186" s="50">
+      <c r="O201" s="92">
+        <v>154185</v>
+      </c>
+      <c r="P201" s="92"/>
+      <c r="Q201" s="92" t="s">
+        <v>235</v>
+      </c>
+      <c r="R201" s="92"/>
+    </row>
+    <row r="202" spans="1:18">
+      <c r="A202" s="100">
+        <v>201</v>
+      </c>
+      <c r="B202" s="5">
+        <v>2026</v>
+      </c>
+      <c r="D202" s="5">
+        <v>2</v>
+      </c>
+      <c r="E202" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="F202" s="5">
         <v>9</v>
       </c>
-      <c r="M186" s="50"/>
-      <c r="N186" s="50" t="s">
-        <v>347</v>
-      </c>
-      <c r="O186" s="108">
-        <v>148758</v>
-      </c>
-      <c r="P186" s="109">
-        <v>69870</v>
-      </c>
-      <c r="Q186" s="50" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="187" spans="1:31">
-      <c r="J187" s="21"/>
-      <c r="M187" s="21"/>
-    </row>
-    <row r="188" spans="1:31">
-      <c r="J188" s="21"/>
-      <c r="M188" s="21"/>
-    </row>
-    <row r="189" spans="1:31">
-      <c r="J189" s="21"/>
-      <c r="M189" s="21"/>
-    </row>
-    <row r="190" spans="1:31">
-      <c r="J190" s="21"/>
-      <c r="M190" s="21"/>
-    </row>
-    <row r="191" spans="1:31">
-      <c r="J191" s="21"/>
-      <c r="M191" s="21"/>
-    </row>
-    <row r="192" spans="1:31">
-      <c r="J192" s="21"/>
-      <c r="M192" s="21"/>
-    </row>
-    <row r="193" spans="10:13">
-      <c r="J193" s="21"/>
-      <c r="M193" s="21"/>
-    </row>
-    <row r="194" spans="10:13">
-      <c r="J194" s="21"/>
-      <c r="M194" s="21"/>
-    </row>
-    <row r="195" spans="10:13">
-      <c r="J195" s="21"/>
-      <c r="M195" s="21"/>
-    </row>
-    <row r="196" spans="10:13">
-      <c r="J196" s="21"/>
-      <c r="M196" s="21"/>
-    </row>
-    <row r="197" spans="10:13">
-      <c r="J197" s="21"/>
-      <c r="M197" s="21"/>
-    </row>
-    <row r="198" spans="10:13">
-      <c r="J198" s="21"/>
-      <c r="M198" s="21"/>
-    </row>
-    <row r="199" spans="10:13">
-      <c r="J199" s="21"/>
-      <c r="M199" s="21"/>
-    </row>
-    <row r="200" spans="10:13">
-      <c r="J200" s="21"/>
-      <c r="M200" s="21"/>
-    </row>
-    <row r="201" spans="10:13">
-      <c r="J201" s="21"/>
-      <c r="M201" s="21"/>
-    </row>
-    <row r="202" spans="10:13">
-      <c r="J202" s="21"/>
+      <c r="G202" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H202" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I202" s="11" t="s">
+        <v>376</v>
+      </c>
+      <c r="J202" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="K202" s="5">
+        <v>9</v>
+      </c>
+      <c r="L202" s="5">
+        <v>10</v>
+      </c>
       <c r="M202" s="21"/>
-    </row>
-    <row r="203" spans="10:13">
-      <c r="J203" s="21"/>
+      <c r="N202" s="5" t="s">
+        <v>352</v>
+      </c>
+      <c r="O202" s="92">
+        <v>154488</v>
+      </c>
+      <c r="P202" s="92">
+        <v>85937</v>
+      </c>
+      <c r="Q202" s="92" t="s">
+        <v>187</v>
+      </c>
+      <c r="R202" s="92"/>
+    </row>
+    <row r="203" spans="1:18" ht="30">
+      <c r="A203" s="100">
+        <v>202</v>
+      </c>
+      <c r="B203" s="5">
+        <v>2026</v>
+      </c>
+      <c r="D203" s="5">
+        <v>2</v>
+      </c>
+      <c r="E203" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="F203" s="5">
+        <v>10</v>
+      </c>
+      <c r="G203" s="5" t="s">
+        <v>501</v>
+      </c>
+      <c r="H203" s="5" t="s">
+        <v>501</v>
+      </c>
+      <c r="I203" s="11" t="s">
+        <v>502</v>
+      </c>
+      <c r="J203" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="K203" s="5">
+        <v>10</v>
+      </c>
+      <c r="L203" s="5">
+        <v>10</v>
+      </c>
       <c r="M203" s="21"/>
-    </row>
-    <row r="204" spans="10:13">
-      <c r="J204" s="21"/>
+      <c r="N203" s="5" t="s">
+        <v>352</v>
+      </c>
+      <c r="O203">
+        <v>156238</v>
+      </c>
+      <c r="Q203" s="5" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="204" spans="1:18" hidden="1">
+      <c r="A204" s="100">
+        <v>203</v>
+      </c>
       <c r="M204" s="21"/>
     </row>
-    <row r="205" spans="10:13">
-      <c r="J205" s="21"/>
+    <row r="205" spans="1:18" hidden="1">
+      <c r="A205" s="100">
+        <v>204</v>
+      </c>
       <c r="M205" s="21"/>
     </row>
-    <row r="206" spans="10:13">
-      <c r="J206" s="21"/>
+    <row r="206" spans="1:18" hidden="1">
+      <c r="A206" s="100">
+        <v>205</v>
+      </c>
       <c r="M206" s="21"/>
     </row>
-    <row r="207" spans="10:13">
-      <c r="J207" s="21"/>
+    <row r="207" spans="1:18" hidden="1">
+      <c r="A207" s="100">
+        <v>206</v>
+      </c>
       <c r="M207" s="21"/>
     </row>
-    <row r="208" spans="10:13">
-      <c r="J208" s="21"/>
+    <row r="208" spans="1:18" hidden="1">
+      <c r="A208" s="100">
+        <v>207</v>
+      </c>
       <c r="M208" s="21"/>
     </row>
-    <row r="209" spans="10:13">
-      <c r="J209" s="21"/>
+    <row r="209" spans="1:13" hidden="1">
+      <c r="A209" s="100">
+        <v>208</v>
+      </c>
       <c r="M209" s="21"/>
     </row>
-    <row r="210" spans="10:13">
-      <c r="J210" s="21"/>
+    <row r="210" spans="1:13">
+      <c r="A210" s="5"/>
       <c r="M210" s="21"/>
     </row>
-    <row r="211" spans="10:13">
-      <c r="J211" s="21"/>
+    <row r="211" spans="1:13">
+      <c r="A211" s="5"/>
       <c r="M211" s="21"/>
     </row>
-    <row r="212" spans="10:13">
-      <c r="J212" s="21"/>
+    <row r="212" spans="1:13">
+      <c r="A212" s="5"/>
       <c r="M212" s="21"/>
     </row>
-    <row r="213" spans="10:13">
-      <c r="J213" s="21"/>
+    <row r="213" spans="1:13">
+      <c r="A213" s="5"/>
       <c r="M213" s="21"/>
     </row>
-    <row r="214" spans="10:13">
-      <c r="J214" s="21"/>
+    <row r="214" spans="1:13">
+      <c r="A214" s="5"/>
       <c r="M214" s="21"/>
     </row>
-    <row r="215" spans="10:13">
-      <c r="J215" s="21"/>
+    <row r="215" spans="1:13">
+      <c r="A215" s="5"/>
       <c r="M215" s="21"/>
     </row>
-    <row r="216" spans="10:13">
-      <c r="J216" s="21"/>
+    <row r="216" spans="1:13">
+      <c r="A216" s="5"/>
       <c r="M216" s="21"/>
     </row>
-    <row r="217" spans="10:13">
-      <c r="J217" s="21"/>
+    <row r="217" spans="1:13">
+      <c r="A217" s="5"/>
       <c r="M217" s="21"/>
     </row>
-    <row r="218" spans="10:13">
-      <c r="J218" s="21"/>
+    <row r="218" spans="1:13">
+      <c r="A218" s="5"/>
       <c r="M218" s="21"/>
     </row>
-    <row r="219" spans="10:13">
-      <c r="J219" s="21"/>
+    <row r="219" spans="1:13">
+      <c r="A219" s="5"/>
       <c r="M219" s="21"/>
     </row>
-    <row r="220" spans="10:13">
-      <c r="J220" s="21"/>
+    <row r="220" spans="1:13">
+      <c r="A220" s="5"/>
       <c r="M220" s="21"/>
     </row>
-    <row r="221" spans="10:13">
-      <c r="J221" s="21"/>
+    <row r="221" spans="1:13">
+      <c r="A221" s="5"/>
       <c r="M221" s="21"/>
     </row>
-    <row r="222" spans="10:13">
-      <c r="J222" s="21"/>
+    <row r="222" spans="1:13">
+      <c r="A222" s="5"/>
       <c r="M222" s="21"/>
     </row>
-    <row r="223" spans="10:13">
-      <c r="J223" s="21"/>
+    <row r="223" spans="1:13">
+      <c r="A223" s="5"/>
       <c r="M223" s="21"/>
     </row>
-    <row r="224" spans="10:13">
-      <c r="J224" s="21"/>
+    <row r="224" spans="1:13">
+      <c r="A224" s="5"/>
       <c r="M224" s="21"/>
     </row>
-    <row r="225" spans="10:13">
-      <c r="J225" s="21"/>
+    <row r="225" spans="1:13">
+      <c r="A225" s="5"/>
       <c r="M225" s="21"/>
     </row>
-    <row r="226" spans="10:13">
-      <c r="J226" s="21"/>
+    <row r="226" spans="1:13">
       <c r="M226" s="21"/>
     </row>
-    <row r="227" spans="10:13">
-      <c r="J227" s="21"/>
+    <row r="227" spans="1:13">
       <c r="M227" s="21"/>
     </row>
-    <row r="228" spans="10:13">
-      <c r="J228" s="21"/>
+    <row r="228" spans="1:13">
       <c r="M228" s="21"/>
     </row>
-    <row r="229" spans="10:13">
-      <c r="J229" s="21"/>
+    <row r="229" spans="1:13">
       <c r="M229" s="21"/>
     </row>
-    <row r="230" spans="10:13">
-      <c r="J230" s="21"/>
+    <row r="230" spans="1:13">
       <c r="M230" s="21"/>
     </row>
-    <row r="231" spans="10:13">
-      <c r="J231" s="21"/>
+    <row r="231" spans="1:13">
       <c r="M231" s="21"/>
     </row>
-    <row r="232" spans="10:13">
-      <c r="J232" s="21"/>
+    <row r="232" spans="1:13">
       <c r="M232" s="21"/>
     </row>
-    <row r="233" spans="10:13">
-      <c r="J233" s="21"/>
+    <row r="233" spans="1:13">
       <c r="M233" s="21"/>
     </row>
-    <row r="234" spans="10:13">
-      <c r="J234" s="21"/>
+    <row r="234" spans="1:13">
       <c r="M234" s="21"/>
     </row>
-    <row r="235" spans="10:13">
-      <c r="J235" s="21"/>
+    <row r="235" spans="1:13">
       <c r="M235" s="21"/>
     </row>
-    <row r="236" spans="10:13">
-      <c r="J236" s="21"/>
+    <row r="236" spans="1:13">
       <c r="M236" s="21"/>
     </row>
-    <row r="237" spans="10:13">
-      <c r="J237" s="21"/>
+    <row r="237" spans="1:13">
       <c r="M237" s="21"/>
     </row>
-    <row r="238" spans="10:13">
-      <c r="J238" s="21"/>
+    <row r="238" spans="1:13">
       <c r="M238" s="21"/>
     </row>
-    <row r="239" spans="10:13">
-      <c r="J239" s="21"/>
+    <row r="239" spans="1:13">
       <c r="M239" s="21"/>
     </row>
-    <row r="240" spans="10:13">
-      <c r="J240" s="21"/>
+    <row r="240" spans="1:13">
       <c r="M240" s="21"/>
     </row>
-    <row r="241" spans="10:13">
-      <c r="J241" s="21"/>
+    <row r="241" spans="13:13">
       <c r="M241" s="21"/>
     </row>
-    <row r="242" spans="10:13">
-      <c r="J242" s="21"/>
+    <row r="242" spans="13:13">
       <c r="M242" s="21"/>
     </row>
-    <row r="243" spans="10:13">
-      <c r="J243" s="21"/>
+    <row r="243" spans="13:13">
       <c r="M243" s="21"/>
     </row>
-    <row r="244" spans="10:13">
-      <c r="J244" s="21"/>
+    <row r="244" spans="13:13">
       <c r="M244" s="21"/>
     </row>
-    <row r="245" spans="10:13">
-      <c r="J245" s="21"/>
+    <row r="245" spans="13:13">
       <c r="M245" s="21"/>
     </row>
-    <row r="246" spans="10:13">
-      <c r="J246" s="21"/>
+    <row r="246" spans="13:13">
       <c r="M246" s="21"/>
     </row>
-    <row r="247" spans="10:13">
-      <c r="J247" s="21"/>
+    <row r="247" spans="13:13">
       <c r="M247" s="21"/>
     </row>
-    <row r="248" spans="10:13">
-      <c r="J248" s="21"/>
+    <row r="248" spans="13:13">
       <c r="M248" s="21"/>
     </row>
-    <row r="249" spans="10:13">
-      <c r="J249" s="21"/>
-      <c r="M249" s="21"/>
-    </row>
-    <row r="250" spans="10:13">
-      <c r="J250" s="21"/>
-      <c r="M250" s="21"/>
-    </row>
-    <row r="251" spans="10:13">
-      <c r="J251" s="21"/>
-      <c r="M251" s="21"/>
-    </row>
-    <row r="252" spans="10:13">
-      <c r="J252" s="21"/>
-      <c r="M252" s="21"/>
-    </row>
-    <row r="253" spans="10:13">
-      <c r="J253" s="21"/>
-      <c r="M253" s="21"/>
-    </row>
-    <row r="254" spans="10:13">
-      <c r="J254" s="21"/>
-      <c r="M254" s="21"/>
-    </row>
-    <row r="255" spans="10:13">
-      <c r="J255" s="21"/>
-      <c r="M255" s="21"/>
-    </row>
-    <row r="256" spans="10:13">
-      <c r="J256" s="21"/>
-      <c r="M256" s="21"/>
-    </row>
-    <row r="257" spans="10:13">
-      <c r="J257" s="21"/>
-      <c r="M257" s="21"/>
-    </row>
-    <row r="258" spans="10:13">
-      <c r="J258" s="21"/>
-      <c r="M258" s="21"/>
-    </row>
-    <row r="259" spans="10:13">
-      <c r="J259" s="21"/>
-      <c r="M259" s="21"/>
-    </row>
-    <row r="260" spans="10:13">
-      <c r="J260" s="21"/>
-      <c r="M260" s="21"/>
-    </row>
-    <row r="261" spans="10:13">
-      <c r="J261" s="21"/>
-      <c r="M261" s="21"/>
-    </row>
-    <row r="262" spans="10:13">
-      <c r="J262" s="21"/>
-      <c r="M262" s="21"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:V186" xr:uid="{51912A95-8495-48EF-8281-9EA7F885C6C0}">
+  <autoFilter ref="A1:V209" xr:uid="{51912A95-8495-48EF-8281-9EA7F885C6C0}">
     <filterColumn colId="1">
       <filters>
         <filter val="2026"/>
       </filters>
     </filterColumn>
+    <filterColumn colId="13">
+      <filters>
+        <filter val="Escalado a desarrollo"/>
+      </filters>
+    </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="D1:E1048576 Q160:Q161">
-    <cfRule type="cellIs" dxfId="81" priority="58" operator="equal">
-      <formula>1</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="80" priority="56" operator="equal">
+  <conditionalFormatting sqref="Q160:Q161 D1:E1048576">
+    <cfRule type="cellIs" dxfId="89" priority="69" operator="equal">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="79" priority="57" operator="equal">
+    <cfRule type="cellIs" dxfId="88" priority="70" operator="equal">
       <formula>2</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="87" priority="71" operator="equal">
+      <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M139">
-    <cfRule type="cellIs" dxfId="78" priority="43" operator="equal">
+    <cfRule type="cellIs" dxfId="86" priority="56" operator="equal">
       <formula>"en regional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="77" priority="44" operator="equal">
+    <cfRule type="cellIs" dxfId="85" priority="57" operator="equal">
       <formula>"regional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="76" priority="45" operator="equal">
+    <cfRule type="cellIs" dxfId="84" priority="58" operator="equal">
       <formula>"asignado a dev"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="75" priority="46" operator="equal">
+    <cfRule type="cellIs" dxfId="83" priority="59" operator="equal">
       <formula>"seguimiento soporte"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="74" priority="47" operator="equal">
+    <cfRule type="cellIs" dxfId="82" priority="60" operator="equal">
       <formula>"solventado"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M162">
-    <cfRule type="cellIs" dxfId="73" priority="35" operator="equal">
+    <cfRule type="cellIs" dxfId="81" priority="48" operator="equal">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="72" priority="36" operator="equal">
+    <cfRule type="cellIs" dxfId="80" priority="49" operator="equal">
       <formula>2</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="71" priority="37" operator="equal">
+    <cfRule type="cellIs" dxfId="79" priority="50" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M163:M169 AF163:AF169">
-    <cfRule type="cellIs" dxfId="70" priority="28" operator="equal">
-      <formula>"produccion"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="69" priority="24" operator="equal">
+  <conditionalFormatting sqref="M163:M169 AF163:AF169 N2:N1048576">
+    <cfRule type="cellIs" dxfId="78" priority="37" operator="equal">
       <formula>"en regional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="68" priority="25" operator="equal">
+    <cfRule type="cellIs" dxfId="77" priority="38" operator="equal">
       <formula>"regional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="67" priority="26" operator="equal">
+    <cfRule type="cellIs" dxfId="76" priority="39" operator="equal">
       <formula>"Escalado a desarrollo"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="66" priority="27" operator="equal">
+    <cfRule type="cellIs" dxfId="75" priority="40" operator="equal">
       <formula>"reapertura"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="74" priority="41" operator="equal">
+      <formula>"produccion"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M180 AB180">
-    <cfRule type="cellIs" dxfId="65" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="73" priority="17" operator="equal">
       <formula>"en regional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="64" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="72" priority="18" operator="equal">
       <formula>"regional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="63" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="71" priority="19" operator="equal">
       <formula>"Escalado a desarrollo"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="62" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="70" priority="20" operator="equal">
       <formula>"reapertura"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="61" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="69" priority="21" operator="equal">
       <formula>"produccion"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N1048576 M156">
-    <cfRule type="cellIs" dxfId="60" priority="38" operator="equal">
+  <conditionalFormatting sqref="M187 AP187">
+    <cfRule type="cellIs" dxfId="68" priority="9" operator="equal">
       <formula>"en regional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="59" priority="39" operator="equal">
+    <cfRule type="cellIs" dxfId="67" priority="10" operator="equal">
       <formula>"regional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="58" priority="40" operator="equal">
+    <cfRule type="cellIs" dxfId="66" priority="11" operator="equal">
       <formula>"Escalado a desarrollo"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="57" priority="41" operator="equal">
+    <cfRule type="cellIs" dxfId="65" priority="12" operator="equal">
       <formula>"reapertura"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="56" priority="42" operator="equal">
+    <cfRule type="cellIs" dxfId="64" priority="13" operator="equal">
+      <formula>"produccion"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M156">
+    <cfRule type="cellIs" dxfId="63" priority="51" operator="equal">
+      <formula>"en regional"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="62" priority="52" operator="equal">
+      <formula>"regional"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="61" priority="53" operator="equal">
+      <formula>"Escalado a desarrollo"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="60" priority="54" operator="equal">
+      <formula>"reapertura"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="59" priority="55" operator="equal">
       <formula>"produccion"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O163:Q172">
-    <cfRule type="cellIs" dxfId="55" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="58" priority="22" operator="equal">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="54" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="57" priority="23" operator="equal">
       <formula>2</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="53" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="56" priority="24" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S180:T180">
-    <cfRule type="cellIs" dxfId="52" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="55" priority="14" operator="equal">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="51" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="54" priority="15" operator="equal">
       <formula>2</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="50" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="53" priority="16" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W163:X169 AI163:AI169">
-    <cfRule type="cellIs" dxfId="49" priority="31" operator="equal">
+    <cfRule type="cellIs" dxfId="52" priority="42" operator="equal">
+      <formula>3</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="51" priority="43" operator="equal">
+      <formula>2</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="50" priority="44" operator="equal">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="48" priority="29" operator="equal">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AG187:AH187">
+    <cfRule type="cellIs" dxfId="49" priority="6" operator="equal">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="47" priority="30" operator="equal">
+    <cfRule type="cellIs" dxfId="48" priority="7" operator="equal">
       <formula>2</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="47" priority="8" operator="equal">
+      <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
@@ -13653,7 +14256,7 @@
         <v>2025</v>
       </c>
       <c r="C2" s="48" t="s">
-        <v>353</v>
+        <v>377</v>
       </c>
       <c r="D2" s="50">
         <v>1</v>
@@ -13668,23 +14271,23 @@
         <v>32</v>
       </c>
       <c r="H2" s="48" t="s">
-        <v>354</v>
+        <v>378</v>
       </c>
       <c r="I2" s="48" t="s">
-        <v>355</v>
+        <v>379</v>
       </c>
       <c r="J2" s="50">
         <v>15</v>
       </c>
       <c r="K2" s="48" t="s">
-        <v>356</v>
+        <v>380</v>
       </c>
       <c r="L2" s="48">
         <v>66708</v>
       </c>
       <c r="M2" s="48"/>
       <c r="N2" s="48" t="s">
-        <v>357</v>
+        <v>381</v>
       </c>
       <c r="O2" s="48"/>
       <c r="P2" s="48" t="s">
@@ -13700,7 +14303,7 @@
         <v>2025</v>
       </c>
       <c r="C3" s="48" t="s">
-        <v>353</v>
+        <v>377</v>
       </c>
       <c r="D3" s="50">
         <v>2</v>
@@ -13715,16 +14318,16 @@
         <v>32</v>
       </c>
       <c r="H3" s="48" t="s">
-        <v>358</v>
+        <v>382</v>
       </c>
       <c r="I3" s="48" t="s">
-        <v>359</v>
+        <v>383</v>
       </c>
       <c r="J3" s="50">
         <v>15</v>
       </c>
       <c r="K3" s="48" t="s">
-        <v>356</v>
+        <v>380</v>
       </c>
       <c r="L3" s="48">
         <v>47326</v>
@@ -13745,7 +14348,7 @@
         <v>2025</v>
       </c>
       <c r="C4" s="48" t="s">
-        <v>353</v>
+        <v>377</v>
       </c>
       <c r="D4" s="50">
         <v>1</v>
@@ -13760,23 +14363,23 @@
         <v>32</v>
       </c>
       <c r="H4" s="48" t="s">
-        <v>360</v>
+        <v>384</v>
       </c>
       <c r="I4" s="48" t="s">
-        <v>361</v>
+        <v>385</v>
       </c>
       <c r="J4" s="50">
         <v>15</v>
       </c>
       <c r="K4" s="48" t="s">
-        <v>356</v>
+        <v>380</v>
       </c>
       <c r="L4" s="48">
         <v>58039</v>
       </c>
       <c r="M4" s="48"/>
       <c r="N4" s="48" t="s">
-        <v>357</v>
+        <v>381</v>
       </c>
       <c r="O4" s="48"/>
       <c r="P4" s="48" t="s">
@@ -13805,27 +14408,27 @@
         <v>32</v>
       </c>
       <c r="H5" s="48" t="s">
-        <v>362</v>
+        <v>386</v>
       </c>
       <c r="I5" s="48" t="s">
-        <v>363</v>
+        <v>387</v>
       </c>
       <c r="J5" s="49">
         <v>14</v>
       </c>
       <c r="K5" s="50" t="s">
-        <v>364</v>
+        <v>388</v>
       </c>
       <c r="L5" s="48">
         <v>62281</v>
       </c>
       <c r="M5" s="48"/>
       <c r="N5" s="48" t="s">
-        <v>363</v>
+        <v>387</v>
       </c>
       <c r="O5" s="48"/>
       <c r="P5" s="48" t="s">
-        <v>365</v>
+        <v>389</v>
       </c>
       <c r="Q5" s="48"/>
     </row>
@@ -13837,7 +14440,7 @@
         <v>2025</v>
       </c>
       <c r="C6" s="48" t="s">
-        <v>353</v>
+        <v>377</v>
       </c>
       <c r="D6" s="50">
         <v>2</v>
@@ -13852,23 +14455,23 @@
         <v>32</v>
       </c>
       <c r="H6" s="48" t="s">
-        <v>366</v>
+        <v>390</v>
       </c>
       <c r="I6" s="48" t="s">
-        <v>359</v>
+        <v>383</v>
       </c>
       <c r="J6" s="50">
         <v>15</v>
       </c>
       <c r="K6" s="48" t="s">
-        <v>356</v>
+        <v>380</v>
       </c>
       <c r="L6" s="48">
         <v>65261</v>
       </c>
       <c r="M6" s="48"/>
       <c r="N6" s="48" t="s">
-        <v>359</v>
+        <v>383</v>
       </c>
       <c r="O6" s="48"/>
       <c r="P6" s="48" t="s">
@@ -13884,7 +14487,7 @@
         <v>2025</v>
       </c>
       <c r="C7" s="48" t="s">
-        <v>353</v>
+        <v>377</v>
       </c>
       <c r="D7" s="50">
         <v>2</v>
@@ -13899,23 +14502,23 @@
         <v>32</v>
       </c>
       <c r="H7" s="48" t="s">
-        <v>367</v>
+        <v>391</v>
       </c>
       <c r="I7" s="48" t="s">
-        <v>363</v>
+        <v>387</v>
       </c>
       <c r="J7" s="50">
         <v>15</v>
       </c>
       <c r="K7" s="48" t="s">
-        <v>356</v>
+        <v>380</v>
       </c>
       <c r="L7" s="48">
         <v>69788</v>
       </c>
       <c r="M7" s="48"/>
       <c r="N7" s="48" t="s">
-        <v>368</v>
+        <v>392</v>
       </c>
       <c r="O7" s="48"/>
       <c r="P7" s="48" t="s">
@@ -13931,7 +14534,7 @@
         <v>2025</v>
       </c>
       <c r="C8" s="48" t="s">
-        <v>369</v>
+        <v>393</v>
       </c>
       <c r="D8" s="50">
         <v>1</v>
@@ -13946,23 +14549,23 @@
         <v>32</v>
       </c>
       <c r="H8" s="48" t="s">
-        <v>370</v>
+        <v>394</v>
       </c>
       <c r="I8" s="48" t="s">
-        <v>361</v>
+        <v>385</v>
       </c>
       <c r="J8" s="50">
         <v>14</v>
       </c>
       <c r="K8" s="50" t="s">
-        <v>364</v>
+        <v>388</v>
       </c>
       <c r="L8" s="48">
         <v>64134</v>
       </c>
       <c r="M8" s="48"/>
       <c r="N8" s="48" t="s">
-        <v>361</v>
+        <v>385</v>
       </c>
       <c r="O8" s="48"/>
       <c r="P8" s="48" t="s">
@@ -13978,7 +14581,7 @@
         <v>2025</v>
       </c>
       <c r="C9" s="48" t="s">
-        <v>369</v>
+        <v>393</v>
       </c>
       <c r="D9" s="50">
         <v>1</v>
@@ -13993,23 +14596,23 @@
         <v>32</v>
       </c>
       <c r="H9" s="48" t="s">
-        <v>371</v>
+        <v>395</v>
       </c>
       <c r="I9" s="48" t="s">
-        <v>359</v>
+        <v>383</v>
       </c>
       <c r="J9" s="50">
         <v>14</v>
       </c>
       <c r="K9" s="50" t="s">
-        <v>364</v>
+        <v>388</v>
       </c>
       <c r="L9" s="48">
         <v>65033</v>
       </c>
       <c r="M9" s="48"/>
       <c r="N9" s="48" t="s">
-        <v>359</v>
+        <v>383</v>
       </c>
       <c r="O9" s="48"/>
       <c r="P9" s="48" t="s">
@@ -14038,25 +14641,25 @@
         <v>32</v>
       </c>
       <c r="H10" s="48" t="s">
-        <v>372</v>
+        <v>396</v>
       </c>
       <c r="I10" s="48" t="s">
-        <v>355</v>
+        <v>379</v>
       </c>
       <c r="J10" s="50"/>
       <c r="K10" s="48" t="s">
-        <v>373</v>
+        <v>397</v>
       </c>
       <c r="L10" s="48">
         <v>67465</v>
       </c>
       <c r="M10" s="48"/>
       <c r="N10" s="48" t="s">
-        <v>355</v>
+        <v>379</v>
       </c>
       <c r="O10" s="48"/>
       <c r="P10" s="48" t="s">
-        <v>365</v>
+        <v>389</v>
       </c>
       <c r="Q10" s="48"/>
     </row>
@@ -14081,25 +14684,25 @@
         <v>32</v>
       </c>
       <c r="H11" s="48" t="s">
-        <v>374</v>
+        <v>398</v>
       </c>
       <c r="I11" s="48" t="s">
-        <v>355</v>
+        <v>379</v>
       </c>
       <c r="J11" s="50"/>
       <c r="K11" s="48" t="s">
-        <v>373</v>
+        <v>397</v>
       </c>
       <c r="L11" s="48">
         <v>73221</v>
       </c>
       <c r="M11" s="48"/>
       <c r="N11" s="48" t="s">
-        <v>355</v>
+        <v>379</v>
       </c>
       <c r="O11" s="48"/>
       <c r="P11" s="48" t="s">
-        <v>365</v>
+        <v>389</v>
       </c>
       <c r="Q11" s="48"/>
     </row>
@@ -14124,21 +14727,21 @@
         <v>32</v>
       </c>
       <c r="H12" s="48" t="s">
-        <v>375</v>
+        <v>399</v>
       </c>
       <c r="I12" s="48" t="s">
-        <v>376</v>
+        <v>400</v>
       </c>
       <c r="J12" s="48"/>
       <c r="K12" s="48" t="s">
-        <v>373</v>
+        <v>397</v>
       </c>
       <c r="L12" s="48">
         <v>76151</v>
       </c>
       <c r="M12" s="48"/>
       <c r="N12" s="48" t="s">
-        <v>377</v>
+        <v>401</v>
       </c>
       <c r="O12" s="48"/>
       <c r="P12" s="48" t="s">
@@ -14167,21 +14770,21 @@
         <v>32</v>
       </c>
       <c r="H13" s="48" t="s">
-        <v>378</v>
+        <v>402</v>
       </c>
       <c r="I13" s="48" t="s">
-        <v>368</v>
+        <v>392</v>
       </c>
       <c r="J13" s="48"/>
       <c r="K13" s="48" t="s">
-        <v>373</v>
+        <v>397</v>
       </c>
       <c r="L13" s="48">
         <v>69301</v>
       </c>
       <c r="M13" s="48"/>
       <c r="N13" s="48" t="s">
-        <v>368</v>
+        <v>392</v>
       </c>
       <c r="O13" s="48"/>
       <c r="P13" s="48" t="s">
@@ -14210,21 +14813,21 @@
         <v>32</v>
       </c>
       <c r="H14" s="48" t="s">
-        <v>379</v>
+        <v>403</v>
       </c>
       <c r="I14" s="48" t="s">
-        <v>363</v>
+        <v>387</v>
       </c>
       <c r="J14" s="48"/>
       <c r="K14" s="48" t="s">
-        <v>373</v>
+        <v>397</v>
       </c>
       <c r="L14" s="48">
         <v>71213</v>
       </c>
       <c r="M14" s="48"/>
       <c r="N14" s="48" t="s">
-        <v>355</v>
+        <v>379</v>
       </c>
       <c r="O14" s="48"/>
       <c r="P14" s="48" t="s">
@@ -14253,25 +14856,25 @@
         <v>32</v>
       </c>
       <c r="H15" s="48" t="s">
-        <v>380</v>
+        <v>404</v>
       </c>
       <c r="I15" s="48" t="s">
-        <v>381</v>
+        <v>405</v>
       </c>
       <c r="J15" s="48"/>
       <c r="K15" s="48" t="s">
-        <v>373</v>
+        <v>397</v>
       </c>
       <c r="L15" s="48">
         <v>74017</v>
       </c>
       <c r="M15" s="48"/>
       <c r="N15" s="48" t="s">
-        <v>368</v>
+        <v>392</v>
       </c>
       <c r="O15" s="48"/>
       <c r="P15" s="48" t="s">
-        <v>365</v>
+        <v>389</v>
       </c>
       <c r="Q15" s="48"/>
     </row>
@@ -14296,21 +14899,21 @@
         <v>32</v>
       </c>
       <c r="H16" s="48" t="s">
-        <v>382</v>
+        <v>406</v>
       </c>
       <c r="I16" s="48" t="s">
-        <v>355</v>
+        <v>379</v>
       </c>
       <c r="J16" s="48"/>
       <c r="K16" s="48" t="s">
-        <v>373</v>
+        <v>397</v>
       </c>
       <c r="L16" s="48">
         <v>60221</v>
       </c>
       <c r="M16" s="48"/>
       <c r="N16" s="48" t="s">
-        <v>355</v>
+        <v>379</v>
       </c>
       <c r="O16" s="48"/>
       <c r="P16" s="48" t="s">
@@ -14339,14 +14942,14 @@
         <v>29</v>
       </c>
       <c r="H17" s="48" t="s">
-        <v>383</v>
+        <v>407</v>
       </c>
       <c r="I17" s="48"/>
       <c r="J17" s="49">
         <v>14</v>
       </c>
       <c r="K17" s="50" t="s">
-        <v>364</v>
+        <v>388</v>
       </c>
       <c r="L17" s="48">
         <v>67792</v>
@@ -14380,14 +14983,14 @@
         <v>29</v>
       </c>
       <c r="H18" s="48" t="s">
-        <v>384</v>
+        <v>408</v>
       </c>
       <c r="I18" s="48"/>
       <c r="J18" s="49">
         <v>14</v>
       </c>
       <c r="K18" s="50" t="s">
-        <v>364</v>
+        <v>388</v>
       </c>
       <c r="L18" s="48">
         <v>67862</v>
@@ -14421,7 +15024,7 @@
         <v>29</v>
       </c>
       <c r="H19" s="48" t="s">
-        <v>385</v>
+        <v>409</v>
       </c>
       <c r="I19" s="48" t="s">
         <v>305</v>
@@ -14430,7 +15033,7 @@
         <v>15</v>
       </c>
       <c r="K19" s="50" t="s">
-        <v>364</v>
+        <v>388</v>
       </c>
       <c r="L19" s="48">
         <v>71854</v>
@@ -14444,7 +15047,7 @@
         <v>96</v>
       </c>
       <c r="Q19" s="48" t="s">
-        <v>386</v>
+        <v>410</v>
       </c>
     </row>
     <row r="20" spans="1:17">
@@ -14468,23 +15071,23 @@
         <v>44</v>
       </c>
       <c r="H20" s="48" t="s">
-        <v>387</v>
+        <v>411</v>
       </c>
       <c r="I20" s="48" t="s">
-        <v>388</v>
+        <v>412</v>
       </c>
       <c r="J20" s="48">
         <v>15</v>
       </c>
       <c r="K20" s="50" t="s">
-        <v>364</v>
+        <v>388</v>
       </c>
       <c r="L20" s="48">
         <v>66111</v>
       </c>
       <c r="M20" s="48"/>
       <c r="N20" s="48" t="s">
-        <v>388</v>
+        <v>412</v>
       </c>
       <c r="O20" s="48"/>
       <c r="P20" s="48" t="s">
@@ -14513,23 +15116,23 @@
         <v>44</v>
       </c>
       <c r="H21" s="48" t="s">
-        <v>389</v>
+        <v>413</v>
       </c>
       <c r="I21" s="48" t="s">
-        <v>388</v>
+        <v>412</v>
       </c>
       <c r="J21" s="48">
         <v>14</v>
       </c>
       <c r="K21" s="50" t="s">
-        <v>364</v>
+        <v>388</v>
       </c>
       <c r="L21" s="48">
         <v>53863</v>
       </c>
       <c r="M21" s="48"/>
       <c r="N21" s="48" t="s">
-        <v>388</v>
+        <v>412</v>
       </c>
       <c r="O21" s="48"/>
       <c r="P21" s="48" t="s">
@@ -14558,23 +15161,23 @@
         <v>44</v>
       </c>
       <c r="H22" s="48" t="s">
-        <v>390</v>
+        <v>414</v>
       </c>
       <c r="I22" s="48" t="s">
-        <v>388</v>
+        <v>412</v>
       </c>
       <c r="J22" s="48">
         <v>15</v>
       </c>
       <c r="K22" s="50" t="s">
-        <v>364</v>
+        <v>388</v>
       </c>
       <c r="L22" s="48">
         <v>52563</v>
       </c>
       <c r="M22" s="48"/>
       <c r="N22" s="48" t="s">
-        <v>355</v>
+        <v>379</v>
       </c>
       <c r="O22" s="48"/>
       <c r="P22" s="48" t="s">
@@ -14603,30 +15206,30 @@
         <v>44</v>
       </c>
       <c r="H23" s="48" t="s">
-        <v>391</v>
+        <v>415</v>
       </c>
       <c r="I23" s="48" t="s">
-        <v>388</v>
+        <v>412</v>
       </c>
       <c r="J23" s="48">
         <v>14</v>
       </c>
       <c r="K23" s="48" t="s">
-        <v>356</v>
+        <v>380</v>
       </c>
       <c r="L23" s="48">
         <v>22271</v>
       </c>
       <c r="M23" s="48"/>
       <c r="N23" s="48" t="s">
-        <v>355</v>
+        <v>379</v>
       </c>
       <c r="O23" s="48"/>
       <c r="P23" s="48" t="s">
         <v>96</v>
       </c>
       <c r="Q23" s="70" t="s">
-        <v>392</v>
+        <v>416</v>
       </c>
     </row>
     <row r="24" spans="1:17" ht="150">
@@ -14650,30 +15253,30 @@
         <v>44</v>
       </c>
       <c r="H24" s="71" t="s">
-        <v>393</v>
+        <v>417</v>
       </c>
       <c r="I24" s="71" t="s">
-        <v>394</v>
+        <v>418</v>
       </c>
       <c r="J24" s="71">
         <v>14</v>
       </c>
       <c r="K24" s="71" t="s">
-        <v>356</v>
+        <v>380</v>
       </c>
       <c r="L24" s="71">
         <v>60957</v>
       </c>
       <c r="M24" s="71"/>
       <c r="N24" s="71" t="s">
-        <v>355</v>
+        <v>379</v>
       </c>
       <c r="O24" s="71"/>
       <c r="P24" s="71" t="s">
         <v>96</v>
       </c>
       <c r="Q24" s="74" t="s">
-        <v>392</v>
+        <v>416</v>
       </c>
     </row>
     <row r="25" spans="1:17" ht="150">
@@ -14697,30 +15300,30 @@
         <v>44</v>
       </c>
       <c r="H25" s="48" t="s">
-        <v>395</v>
+        <v>419</v>
       </c>
       <c r="I25" s="48" t="s">
-        <v>394</v>
+        <v>418</v>
       </c>
       <c r="J25" s="48">
         <v>14</v>
       </c>
       <c r="K25" s="48" t="s">
-        <v>356</v>
+        <v>380</v>
       </c>
       <c r="L25" s="48">
         <v>51984</v>
       </c>
       <c r="M25" s="48"/>
       <c r="N25" s="48" t="s">
-        <v>355</v>
+        <v>379</v>
       </c>
       <c r="O25" s="48"/>
       <c r="P25" s="48" t="s">
         <v>96</v>
       </c>
       <c r="Q25" s="70" t="s">
-        <v>392</v>
+        <v>416</v>
       </c>
     </row>
     <row r="26" spans="1:17">
@@ -14744,30 +15347,30 @@
         <v>44</v>
       </c>
       <c r="H26" s="48" t="s">
-        <v>396</v>
+        <v>420</v>
       </c>
       <c r="I26" s="48" t="s">
-        <v>388</v>
+        <v>412</v>
       </c>
       <c r="J26" s="48">
         <v>15</v>
       </c>
       <c r="K26" s="48" t="s">
-        <v>356</v>
+        <v>380</v>
       </c>
       <c r="L26" s="48">
         <v>71558</v>
       </c>
       <c r="M26" s="48"/>
       <c r="N26" s="48" t="s">
-        <v>355</v>
+        <v>379</v>
       </c>
       <c r="O26" s="48"/>
       <c r="P26" s="48" t="s">
         <v>96</v>
       </c>
       <c r="Q26" s="48" t="s">
-        <v>397</v>
+        <v>421</v>
       </c>
     </row>
     <row r="27" spans="1:17">
@@ -14791,14 +15394,14 @@
         <v>44</v>
       </c>
       <c r="H27" s="48" t="s">
-        <v>398</v>
+        <v>422</v>
       </c>
       <c r="I27" s="48" t="s">
-        <v>399</v>
+        <v>423</v>
       </c>
       <c r="J27" s="48"/>
       <c r="K27" s="48" t="s">
-        <v>400</v>
+        <v>424</v>
       </c>
       <c r="L27" s="48">
         <v>74591</v>
@@ -14830,16 +15433,16 @@
         <v>37</v>
       </c>
       <c r="H28" s="48" t="s">
-        <v>401</v>
+        <v>425</v>
       </c>
       <c r="I28" s="48" t="s">
-        <v>394</v>
+        <v>418</v>
       </c>
       <c r="J28" s="48">
         <v>14</v>
       </c>
       <c r="K28" s="50" t="s">
-        <v>364</v>
+        <v>388</v>
       </c>
       <c r="L28" s="48">
         <v>61667</v>
@@ -14875,16 +15478,16 @@
         <v>37</v>
       </c>
       <c r="H29" s="48" t="s">
-        <v>402</v>
+        <v>426</v>
       </c>
       <c r="I29" s="48" t="s">
-        <v>394</v>
+        <v>418</v>
       </c>
       <c r="J29" s="48">
         <v>14</v>
       </c>
       <c r="K29" s="50" t="s">
-        <v>364</v>
+        <v>388</v>
       </c>
       <c r="L29" s="48">
         <v>57827</v>
@@ -14920,7 +15523,7 @@
         <v>37</v>
       </c>
       <c r="H30" s="48" t="s">
-        <v>403</v>
+        <v>427</v>
       </c>
       <c r="I30" s="48" t="s">
         <v>345</v>
@@ -14929,7 +15532,7 @@
         <v>15</v>
       </c>
       <c r="K30" s="50" t="s">
-        <v>364</v>
+        <v>388</v>
       </c>
       <c r="L30" s="48">
         <v>65259</v>
@@ -14965,16 +15568,16 @@
         <v>37</v>
       </c>
       <c r="H31" s="48" t="s">
-        <v>404</v>
+        <v>428</v>
       </c>
       <c r="I31" s="48" t="s">
-        <v>405</v>
+        <v>429</v>
       </c>
       <c r="J31" s="48">
         <v>15</v>
       </c>
       <c r="K31" s="50" t="s">
-        <v>364</v>
+        <v>388</v>
       </c>
       <c r="L31" s="48">
         <v>65259</v>
@@ -14988,7 +15591,7 @@
         <v>96</v>
       </c>
       <c r="Q31" s="48" t="s">
-        <v>406</v>
+        <v>430</v>
       </c>
     </row>
     <row r="32" spans="1:17">
@@ -15012,16 +15615,16 @@
         <v>37</v>
       </c>
       <c r="H32" s="48" t="s">
-        <v>407</v>
+        <v>431</v>
       </c>
       <c r="I32" s="48" t="s">
-        <v>405</v>
+        <v>429</v>
       </c>
       <c r="J32" s="48">
         <v>15</v>
       </c>
       <c r="K32" s="50" t="s">
-        <v>364</v>
+        <v>388</v>
       </c>
       <c r="L32" s="48">
         <v>71553</v>
@@ -15035,7 +15638,7 @@
         <v>96</v>
       </c>
       <c r="Q32" s="48" t="s">
-        <v>406</v>
+        <v>430</v>
       </c>
     </row>
     <row r="33" spans="1:17">
@@ -15046,7 +15649,7 @@
         <v>2025</v>
       </c>
       <c r="C33" s="48" t="s">
-        <v>408</v>
+        <v>432</v>
       </c>
       <c r="D33" s="50">
         <v>2</v>
@@ -15061,14 +15664,14 @@
         <v>37</v>
       </c>
       <c r="H33" s="48" t="s">
-        <v>409</v>
+        <v>433</v>
       </c>
       <c r="I33" s="48" t="s">
-        <v>410</v>
+        <v>434</v>
       </c>
       <c r="J33" s="48"/>
       <c r="K33" s="48" t="s">
-        <v>373</v>
+        <v>397</v>
       </c>
       <c r="L33" s="48">
         <v>76366</v>
@@ -15091,7 +15694,7 @@
         <v>2025</v>
       </c>
       <c r="C34" s="48" t="s">
-        <v>408</v>
+        <v>432</v>
       </c>
       <c r="D34" s="50">
         <v>2</v>
@@ -15106,23 +15709,23 @@
         <v>26</v>
       </c>
       <c r="H34" s="48" t="s">
-        <v>411</v>
+        <v>435</v>
       </c>
       <c r="I34" s="48" t="s">
-        <v>376</v>
+        <v>400</v>
       </c>
       <c r="J34" s="48">
         <v>16</v>
       </c>
       <c r="K34" s="48" t="s">
-        <v>356</v>
+        <v>380</v>
       </c>
       <c r="L34" s="48">
         <v>67409</v>
       </c>
       <c r="M34" s="48"/>
       <c r="N34" s="48" t="s">
-        <v>412</v>
+        <v>436</v>
       </c>
       <c r="O34" s="48"/>
       <c r="P34" s="48" t="s">
@@ -15138,7 +15741,7 @@
         <v>2025</v>
       </c>
       <c r="C35" s="48" t="s">
-        <v>408</v>
+        <v>432</v>
       </c>
       <c r="D35" s="50">
         <v>2</v>
@@ -15153,23 +15756,23 @@
         <v>26</v>
       </c>
       <c r="H35" s="48" t="s">
-        <v>413</v>
+        <v>437</v>
       </c>
       <c r="I35" s="48" t="s">
-        <v>359</v>
+        <v>383</v>
       </c>
       <c r="J35" s="48">
         <v>16</v>
       </c>
       <c r="K35" s="48" t="s">
-        <v>356</v>
+        <v>380</v>
       </c>
       <c r="L35" s="48">
         <v>66955</v>
       </c>
       <c r="M35" s="48"/>
       <c r="N35" s="48" t="s">
-        <v>368</v>
+        <v>392</v>
       </c>
       <c r="O35" s="48"/>
       <c r="P35" s="48" t="s">
@@ -15185,7 +15788,7 @@
         <v>2025</v>
       </c>
       <c r="C36" s="48" t="s">
-        <v>408</v>
+        <v>432</v>
       </c>
       <c r="D36" s="50">
         <v>2</v>
@@ -15200,23 +15803,23 @@
         <v>26</v>
       </c>
       <c r="H36" s="48" t="s">
-        <v>414</v>
+        <v>438</v>
       </c>
       <c r="I36" s="48" t="s">
-        <v>376</v>
+        <v>400</v>
       </c>
       <c r="J36" s="48">
         <v>16</v>
       </c>
       <c r="K36" s="48" t="s">
-        <v>356</v>
+        <v>380</v>
       </c>
       <c r="L36" s="48">
         <v>60856</v>
       </c>
       <c r="M36" s="48"/>
       <c r="N36" s="48" t="s">
-        <v>368</v>
+        <v>392</v>
       </c>
       <c r="O36" s="48"/>
       <c r="P36" s="48" t="s">
@@ -15245,23 +15848,23 @@
         <v>26</v>
       </c>
       <c r="H37" s="48" t="s">
-        <v>415</v>
+        <v>439</v>
       </c>
       <c r="I37" s="48" t="s">
-        <v>376</v>
+        <v>400</v>
       </c>
       <c r="J37" s="48">
         <v>16</v>
       </c>
       <c r="K37" s="48" t="s">
-        <v>373</v>
+        <v>397</v>
       </c>
       <c r="L37" s="48">
         <v>69405</v>
       </c>
       <c r="M37" s="48"/>
       <c r="N37" s="48" t="s">
-        <v>368</v>
+        <v>392</v>
       </c>
       <c r="O37" s="48"/>
       <c r="P37" s="48" t="s">
@@ -15290,23 +15893,23 @@
         <v>26</v>
       </c>
       <c r="H38" s="48" t="s">
-        <v>416</v>
+        <v>440</v>
       </c>
       <c r="I38" s="48" t="s">
-        <v>376</v>
+        <v>400</v>
       </c>
       <c r="J38" s="48">
         <v>15</v>
       </c>
       <c r="K38" s="48" t="s">
-        <v>373</v>
+        <v>397</v>
       </c>
       <c r="L38" s="48">
         <v>68957</v>
       </c>
       <c r="M38" s="48"/>
       <c r="N38" s="48" t="s">
-        <v>368</v>
+        <v>392</v>
       </c>
       <c r="O38" s="48"/>
       <c r="P38" s="48" t="s">
@@ -15335,23 +15938,23 @@
         <v>26</v>
       </c>
       <c r="H39" s="48" t="s">
-        <v>417</v>
+        <v>441</v>
       </c>
       <c r="I39" s="48" t="s">
-        <v>359</v>
+        <v>383</v>
       </c>
       <c r="J39" s="48">
         <v>16</v>
       </c>
       <c r="K39" s="48" t="s">
-        <v>418</v>
+        <v>442</v>
       </c>
       <c r="L39" s="48">
         <v>73439</v>
       </c>
       <c r="M39" s="48"/>
       <c r="N39" s="48" t="s">
-        <v>368</v>
+        <v>392</v>
       </c>
       <c r="O39" s="48"/>
       <c r="P39" s="48" t="s">
@@ -15470,52 +16073,52 @@
   <sheetData>
     <row r="1" spans="1:16" s="21" customFormat="1" ht="30">
       <c r="A1" s="40" t="s">
-        <v>419</v>
+        <v>443</v>
       </c>
       <c r="B1" s="40" t="s">
-        <v>420</v>
+        <v>444</v>
       </c>
       <c r="C1" s="53" t="s">
-        <v>421</v>
+        <v>445</v>
       </c>
       <c r="D1" s="40" t="s">
-        <v>420</v>
+        <v>444</v>
       </c>
       <c r="E1" s="40" t="s">
-        <v>421</v>
+        <v>445</v>
       </c>
       <c r="F1" s="40" t="s">
         <v>18</v>
       </c>
       <c r="G1" s="40" t="s">
-        <v>422</v>
+        <v>446</v>
       </c>
       <c r="H1" s="41" t="s">
         <v>12</v>
       </c>
       <c r="I1" s="41" t="s">
-        <v>423</v>
+        <v>447</v>
       </c>
       <c r="J1" s="41" t="s">
-        <v>424</v>
+        <v>448</v>
       </c>
       <c r="K1" s="40" t="s">
-        <v>425</v>
+        <v>449</v>
       </c>
       <c r="L1" s="40" t="s">
-        <v>426</v>
+        <v>450</v>
       </c>
       <c r="M1" s="40" t="s">
-        <v>427</v>
+        <v>451</v>
       </c>
       <c r="N1" s="40" t="s">
-        <v>428</v>
+        <v>452</v>
       </c>
       <c r="O1" s="40" t="s">
-        <v>429</v>
+        <v>453</v>
       </c>
       <c r="P1" s="56" t="s">
-        <v>430</v>
+        <v>454</v>
       </c>
     </row>
     <row r="2" spans="1:16" ht="30">
@@ -15527,16 +16130,16 @@
       </c>
       <c r="E2" s="65"/>
       <c r="F2" s="66" t="s">
-        <v>431</v>
+        <v>455</v>
       </c>
       <c r="G2" s="67" t="s">
-        <v>432</v>
+        <v>456</v>
       </c>
       <c r="H2" s="68">
         <v>45762.474999999999</v>
       </c>
       <c r="I2" s="66" t="s">
-        <v>433</v>
+        <v>457</v>
       </c>
       <c r="J2" s="66">
         <v>133</v>
@@ -15547,7 +16150,7 @@
         <v>61</v>
       </c>
       <c r="N2" s="66" t="s">
-        <v>434</v>
+        <v>458</v>
       </c>
       <c r="O2" s="55">
         <f>+J2-M2</f>
@@ -15567,16 +16170,16 @@
       </c>
       <c r="E3" s="54"/>
       <c r="F3" s="42" t="s">
-        <v>431</v>
+        <v>455</v>
       </c>
       <c r="G3" s="43" t="s">
-        <v>435</v>
+        <v>459</v>
       </c>
       <c r="H3" s="51">
         <v>45819.472222222219</v>
       </c>
       <c r="I3" s="42" t="s">
-        <v>436</v>
+        <v>460</v>
       </c>
       <c r="J3" s="42">
         <v>1</v>
@@ -15586,7 +16189,7 @@
         <v>1</v>
       </c>
       <c r="N3" s="42" t="s">
-        <v>434</v>
+        <v>458</v>
       </c>
       <c r="O3" s="6">
         <f t="shared" ref="O3:O28" si="1">+J3-M3</f>
@@ -15606,16 +16209,16 @@
       </c>
       <c r="E4" s="54"/>
       <c r="F4" s="42" t="s">
-        <v>431</v>
+        <v>455</v>
       </c>
       <c r="G4" s="43" t="s">
-        <v>437</v>
+        <v>461</v>
       </c>
       <c r="H4" s="51">
         <v>45649.487500000003</v>
       </c>
       <c r="I4" s="42" t="s">
-        <v>438</v>
+        <v>462</v>
       </c>
       <c r="J4" s="42">
         <v>1</v>
@@ -15624,13 +16227,13 @@
         <v>45681.463888888888</v>
       </c>
       <c r="L4" s="6" t="s">
-        <v>438</v>
+        <v>462</v>
       </c>
       <c r="M4" s="6">
         <v>1</v>
       </c>
       <c r="N4" s="42" t="s">
-        <v>439</v>
+        <v>463</v>
       </c>
       <c r="O4" s="6">
         <f t="shared" si="1"/>
@@ -15650,16 +16253,16 @@
       </c>
       <c r="E5" s="54"/>
       <c r="F5" s="42" t="s">
-        <v>431</v>
+        <v>455</v>
       </c>
       <c r="G5" s="43" t="s">
-        <v>440</v>
+        <v>464</v>
       </c>
       <c r="H5" s="51">
         <v>45667.594444444447</v>
       </c>
       <c r="I5" s="42" t="s">
-        <v>438</v>
+        <v>462</v>
       </c>
       <c r="J5" s="42">
         <v>1</v>
@@ -15668,13 +16271,13 @@
         <v>45681.491666666669</v>
       </c>
       <c r="L5" s="6" t="s">
-        <v>438</v>
+        <v>462</v>
       </c>
       <c r="M5" s="6">
         <v>1</v>
       </c>
       <c r="N5" s="42" t="s">
-        <v>439</v>
+        <v>463</v>
       </c>
       <c r="O5" s="6">
         <f t="shared" si="1"/>
@@ -15694,16 +16297,16 @@
       </c>
       <c r="E6" s="54"/>
       <c r="F6" s="42" t="s">
-        <v>431</v>
+        <v>455</v>
       </c>
       <c r="G6" s="43" t="s">
-        <v>441</v>
+        <v>465</v>
       </c>
       <c r="H6" s="51">
         <v>45691.732638888891</v>
       </c>
       <c r="I6" s="42" t="s">
-        <v>442</v>
+        <v>466</v>
       </c>
       <c r="J6" s="42">
         <v>1</v>
@@ -15712,13 +16315,13 @@
         <v>45695.411805555559</v>
       </c>
       <c r="L6" s="6" t="s">
-        <v>442</v>
+        <v>466</v>
       </c>
       <c r="M6" s="6">
         <v>1</v>
       </c>
       <c r="N6" s="42" t="s">
-        <v>439</v>
+        <v>463</v>
       </c>
       <c r="O6" s="6">
         <f t="shared" si="1"/>
@@ -15738,16 +16341,16 @@
       </c>
       <c r="E7" s="54"/>
       <c r="F7" s="42" t="s">
-        <v>431</v>
+        <v>455</v>
       </c>
       <c r="G7" s="43" t="s">
-        <v>443</v>
+        <v>467</v>
       </c>
       <c r="H7" s="51">
         <v>45698.453472222223</v>
       </c>
       <c r="I7" s="42" t="s">
-        <v>442</v>
+        <v>466</v>
       </c>
       <c r="J7" s="42">
         <v>1</v>
@@ -15756,13 +16359,13 @@
         <v>45712.490277777775</v>
       </c>
       <c r="L7" s="6" t="s">
-        <v>442</v>
+        <v>466</v>
       </c>
       <c r="M7" s="6">
         <v>1</v>
       </c>
       <c r="N7" s="42" t="s">
-        <v>439</v>
+        <v>463</v>
       </c>
       <c r="O7" s="6">
         <f t="shared" si="1"/>
@@ -15782,16 +16385,16 @@
       </c>
       <c r="E8" s="54"/>
       <c r="F8" s="42" t="s">
-        <v>431</v>
+        <v>455</v>
       </c>
       <c r="G8" s="43" t="s">
-        <v>444</v>
+        <v>468</v>
       </c>
       <c r="H8" s="51">
         <v>45706.435416666667</v>
       </c>
       <c r="I8" s="42" t="s">
-        <v>442</v>
+        <v>466</v>
       </c>
       <c r="J8" s="42">
         <v>1</v>
@@ -15800,13 +16403,13 @@
         <v>45712.429166666669</v>
       </c>
       <c r="L8" s="6" t="s">
-        <v>442</v>
+        <v>466</v>
       </c>
       <c r="M8" s="6">
         <v>1</v>
       </c>
       <c r="N8" s="42" t="s">
-        <v>439</v>
+        <v>463</v>
       </c>
       <c r="O8" s="6">
         <f t="shared" si="1"/>
@@ -15826,16 +16429,16 @@
       </c>
       <c r="E9" s="59"/>
       <c r="F9" s="60" t="s">
-        <v>431</v>
+        <v>455</v>
       </c>
       <c r="G9" s="61" t="s">
-        <v>445</v>
+        <v>469</v>
       </c>
       <c r="H9" s="62">
         <v>45706.447222222225</v>
       </c>
       <c r="I9" s="60" t="s">
-        <v>442</v>
+        <v>466</v>
       </c>
       <c r="J9" s="60">
         <v>1</v>
@@ -15844,13 +16447,13 @@
         <v>45740.695833333331</v>
       </c>
       <c r="L9" s="63" t="s">
-        <v>446</v>
+        <v>470</v>
       </c>
       <c r="M9" s="63">
         <v>1</v>
       </c>
       <c r="N9" s="60" t="s">
-        <v>439</v>
+        <v>463</v>
       </c>
       <c r="O9" s="63">
         <f t="shared" si="1"/>
@@ -15870,16 +16473,16 @@
       </c>
       <c r="E10" s="42"/>
       <c r="F10" s="42" t="s">
-        <v>431</v>
+        <v>455</v>
       </c>
       <c r="G10" s="43" t="s">
-        <v>447</v>
+        <v>471</v>
       </c>
       <c r="H10" s="51">
         <v>45714.780555555553</v>
       </c>
       <c r="I10" s="42" t="s">
-        <v>446</v>
+        <v>470</v>
       </c>
       <c r="J10" s="42">
         <v>1</v>
@@ -15888,13 +16491,13 @@
         <v>45740.696527777778</v>
       </c>
       <c r="L10" s="6" t="s">
-        <v>446</v>
+        <v>470</v>
       </c>
       <c r="M10" s="6">
         <v>1</v>
       </c>
       <c r="N10" s="42" t="s">
-        <v>439</v>
+        <v>463</v>
       </c>
       <c r="O10" s="6">
         <f t="shared" si="1"/>
@@ -15914,16 +16517,16 @@
       </c>
       <c r="E11" s="42"/>
       <c r="F11" s="42" t="s">
-        <v>431</v>
+        <v>455</v>
       </c>
       <c r="G11" s="43" t="s">
-        <v>448</v>
+        <v>472</v>
       </c>
       <c r="H11" s="51">
         <v>45714.785416666666</v>
       </c>
       <c r="I11" s="42" t="s">
-        <v>446</v>
+        <v>470</v>
       </c>
       <c r="J11" s="42">
         <v>1</v>
@@ -15932,13 +16535,13 @@
         <v>45740.696527777778</v>
       </c>
       <c r="L11" s="6" t="s">
-        <v>446</v>
+        <v>470</v>
       </c>
       <c r="M11" s="6">
         <v>1</v>
       </c>
       <c r="N11" s="42" t="s">
-        <v>439</v>
+        <v>463</v>
       </c>
       <c r="O11" s="6">
         <f t="shared" si="1"/>
@@ -15958,16 +16561,16 @@
       </c>
       <c r="E12" s="42"/>
       <c r="F12" s="42" t="s">
-        <v>431</v>
+        <v>455</v>
       </c>
       <c r="G12" s="43" t="s">
-        <v>449</v>
+        <v>473</v>
       </c>
       <c r="H12" s="51">
         <v>45721.500694444447</v>
       </c>
       <c r="I12" s="42" t="s">
-        <v>446</v>
+        <v>470</v>
       </c>
       <c r="J12" s="42">
         <v>144</v>
@@ -15976,13 +16579,13 @@
         <v>45740.699305555558</v>
       </c>
       <c r="L12" s="6" t="s">
-        <v>446</v>
+        <v>470</v>
       </c>
       <c r="M12" s="6">
         <v>45</v>
       </c>
       <c r="N12" s="42" t="s">
-        <v>439</v>
+        <v>463</v>
       </c>
       <c r="O12" s="6">
         <f t="shared" si="1"/>
@@ -16002,16 +16605,16 @@
       </c>
       <c r="E13" s="65"/>
       <c r="F13" s="66" t="s">
-        <v>431</v>
+        <v>455</v>
       </c>
       <c r="G13" s="67" t="s">
-        <v>450</v>
+        <v>474</v>
       </c>
       <c r="H13" s="68">
         <v>45744.413194444445</v>
       </c>
       <c r="I13" s="66" t="s">
-        <v>433</v>
+        <v>457</v>
       </c>
       <c r="J13" s="66">
         <v>1</v>
@@ -16020,13 +16623,13 @@
         <v>45754.729166666664</v>
       </c>
       <c r="L13" s="55" t="s">
-        <v>433</v>
+        <v>457</v>
       </c>
       <c r="M13" s="55">
         <v>1</v>
       </c>
       <c r="N13" s="66" t="s">
-        <v>439</v>
+        <v>463</v>
       </c>
       <c r="O13" s="55">
         <f t="shared" si="1"/>
@@ -16046,16 +16649,16 @@
       </c>
       <c r="E14" s="54"/>
       <c r="F14" s="42" t="s">
-        <v>431</v>
+        <v>455</v>
       </c>
       <c r="G14" s="43" t="s">
-        <v>451</v>
+        <v>475</v>
       </c>
       <c r="H14" s="51">
         <v>45754.454861111109</v>
       </c>
       <c r="I14" s="42" t="s">
-        <v>433</v>
+        <v>457</v>
       </c>
       <c r="J14" s="42">
         <v>1</v>
@@ -16064,13 +16667,13 @@
         <v>45792.43472222222</v>
       </c>
       <c r="L14" s="6" t="s">
-        <v>452</v>
+        <v>476</v>
       </c>
       <c r="M14" s="6">
         <v>1</v>
       </c>
       <c r="N14" s="42" t="s">
-        <v>439</v>
+        <v>463</v>
       </c>
       <c r="O14" s="6">
         <f t="shared" si="1"/>
@@ -16090,16 +16693,16 @@
       </c>
       <c r="E15" s="54"/>
       <c r="F15" s="42" t="s">
-        <v>431</v>
+        <v>455</v>
       </c>
       <c r="G15" s="43" t="s">
-        <v>453</v>
+        <v>477</v>
       </c>
       <c r="H15" s="51">
         <v>45762.452777777777</v>
       </c>
       <c r="I15" s="42" t="s">
-        <v>433</v>
+        <v>457</v>
       </c>
       <c r="J15" s="42">
         <v>255</v>
@@ -16108,13 +16711,13 @@
         <v>45799.46875</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>452</v>
+        <v>476</v>
       </c>
       <c r="M15" s="6">
         <v>74</v>
       </c>
       <c r="N15" s="42" t="s">
-        <v>439</v>
+        <v>463</v>
       </c>
       <c r="O15" s="6">
         <f t="shared" si="1"/>
@@ -16134,16 +16737,16 @@
       </c>
       <c r="E16" s="54"/>
       <c r="F16" s="42" t="s">
-        <v>431</v>
+        <v>455</v>
       </c>
       <c r="G16" s="43" t="s">
-        <v>454</v>
+        <v>478</v>
       </c>
       <c r="H16" s="51">
         <v>45771.736111111109</v>
       </c>
       <c r="I16" s="42" t="s">
-        <v>452</v>
+        <v>476</v>
       </c>
       <c r="J16" s="42">
         <v>47</v>
@@ -16152,13 +16755,13 @@
         <v>45785.484722222223</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>452</v>
+        <v>476</v>
       </c>
       <c r="M16" s="6">
         <v>29</v>
       </c>
       <c r="N16" s="42" t="s">
-        <v>439</v>
+        <v>463</v>
       </c>
       <c r="O16" s="6">
         <f t="shared" si="1"/>
@@ -16178,16 +16781,16 @@
       </c>
       <c r="E17" s="54"/>
       <c r="F17" s="42" t="s">
-        <v>431</v>
+        <v>455</v>
       </c>
       <c r="G17" s="43" t="s">
-        <v>455</v>
+        <v>479</v>
       </c>
       <c r="H17" s="51">
         <v>45785.515972222223</v>
       </c>
       <c r="I17" s="42" t="s">
-        <v>452</v>
+        <v>476</v>
       </c>
       <c r="J17" s="42">
         <v>99</v>
@@ -16196,13 +16799,13 @@
         <v>45793.414583333331</v>
       </c>
       <c r="L17" s="6" t="s">
-        <v>452</v>
+        <v>476</v>
       </c>
       <c r="M17" s="6">
         <v>44</v>
       </c>
       <c r="N17" s="42" t="s">
-        <v>439</v>
+        <v>463</v>
       </c>
       <c r="O17" s="6">
         <f t="shared" si="1"/>
@@ -16222,16 +16825,16 @@
       </c>
       <c r="E18" s="54"/>
       <c r="F18" s="42" t="s">
-        <v>431</v>
+        <v>455</v>
       </c>
       <c r="G18" s="43" t="s">
-        <v>456</v>
+        <v>480</v>
       </c>
       <c r="H18" s="51">
         <v>45741.459722222222</v>
       </c>
       <c r="I18" s="42" t="s">
-        <v>433</v>
+        <v>457</v>
       </c>
       <c r="J18" s="42">
         <v>115</v>
@@ -16240,13 +16843,13 @@
         <v>45798.448611111111</v>
       </c>
       <c r="L18" s="6" t="s">
-        <v>452</v>
+        <v>476</v>
       </c>
       <c r="M18" s="6">
         <v>96</v>
       </c>
       <c r="N18" s="42" t="s">
-        <v>439</v>
+        <v>463</v>
       </c>
       <c r="O18" s="6">
         <f t="shared" si="1"/>
@@ -16266,16 +16869,16 @@
       </c>
       <c r="E19" s="54"/>
       <c r="F19" s="42" t="s">
-        <v>431</v>
+        <v>455</v>
       </c>
       <c r="G19" s="43" t="s">
-        <v>457</v>
+        <v>481</v>
       </c>
       <c r="H19" s="51">
         <v>45741.477777777778</v>
       </c>
       <c r="I19" s="42" t="s">
-        <v>433</v>
+        <v>457</v>
       </c>
       <c r="J19" s="42">
         <v>34</v>
@@ -16284,13 +16887,13 @@
         <v>45793.414583333331</v>
       </c>
       <c r="L19" s="6" t="s">
-        <v>452</v>
+        <v>476</v>
       </c>
       <c r="M19" s="6">
         <v>17</v>
       </c>
       <c r="N19" s="42" t="s">
-        <v>439</v>
+        <v>463</v>
       </c>
       <c r="O19" s="6">
         <f t="shared" si="1"/>
@@ -16310,16 +16913,16 @@
       </c>
       <c r="E20" s="54"/>
       <c r="F20" s="42" t="s">
-        <v>458</v>
+        <v>482</v>
       </c>
       <c r="G20" s="43" t="s">
-        <v>459</v>
+        <v>483</v>
       </c>
       <c r="H20" s="51">
         <v>45796.499305555553</v>
       </c>
       <c r="I20" s="42" t="s">
-        <v>452</v>
+        <v>476</v>
       </c>
       <c r="J20" s="42">
         <v>1</v>
@@ -16328,13 +16931,13 @@
         <v>45825.415277777778</v>
       </c>
       <c r="L20" s="6" t="s">
-        <v>436</v>
+        <v>460</v>
       </c>
       <c r="M20" s="6">
         <v>1</v>
       </c>
       <c r="N20" s="42" t="s">
-        <v>439</v>
+        <v>463</v>
       </c>
       <c r="O20" s="6">
         <f t="shared" si="1"/>
@@ -16354,26 +16957,26 @@
       </c>
       <c r="E21" s="54"/>
       <c r="F21" s="42" t="s">
-        <v>431</v>
+        <v>455</v>
       </c>
       <c r="G21" s="43" t="s">
-        <v>460</v>
+        <v>484</v>
       </c>
       <c r="H21" s="51">
         <v>45812.665972222225</v>
       </c>
       <c r="I21" s="42" t="s">
-        <v>436</v>
+        <v>460</v>
       </c>
       <c r="J21" s="42"/>
       <c r="K21" s="51">
         <v>45825.40902777778</v>
       </c>
       <c r="L21" s="6" t="s">
-        <v>436</v>
+        <v>460</v>
       </c>
       <c r="N21" s="42" t="s">
-        <v>439</v>
+        <v>463</v>
       </c>
       <c r="O21" s="6">
         <f t="shared" si="1"/>
@@ -16393,16 +16996,16 @@
       </c>
       <c r="E22" s="54"/>
       <c r="F22" s="42" t="s">
-        <v>431</v>
+        <v>455</v>
       </c>
       <c r="G22" s="43" t="s">
-        <v>461</v>
+        <v>485</v>
       </c>
       <c r="H22" s="51">
         <v>45824.717361111114</v>
       </c>
       <c r="I22" s="42" t="s">
-        <v>436</v>
+        <v>460</v>
       </c>
       <c r="J22" s="42">
         <v>27</v>
@@ -16411,13 +17014,13 @@
         <v>45835.412499999999</v>
       </c>
       <c r="L22" s="6" t="s">
-        <v>462</v>
+        <v>486</v>
       </c>
       <c r="M22" s="6">
         <v>6</v>
       </c>
       <c r="N22" s="42" t="s">
-        <v>439</v>
+        <v>463</v>
       </c>
       <c r="O22" s="6">
         <f t="shared" si="1"/>
@@ -16437,16 +17040,16 @@
       </c>
       <c r="E23" s="54"/>
       <c r="F23" s="42" t="s">
-        <v>431</v>
+        <v>455</v>
       </c>
       <c r="G23" s="43" t="s">
-        <v>463</v>
+        <v>487</v>
       </c>
       <c r="H23" s="51">
         <v>45825.413888888892</v>
       </c>
       <c r="I23" s="42" t="s">
-        <v>436</v>
+        <v>460</v>
       </c>
       <c r="J23" s="42">
         <v>17</v>
@@ -16455,13 +17058,13 @@
         <v>45835.412499999999</v>
       </c>
       <c r="L23" s="6" t="s">
-        <v>462</v>
+        <v>486</v>
       </c>
       <c r="M23" s="6">
         <v>0</v>
       </c>
       <c r="N23" s="42" t="s">
-        <v>439</v>
+        <v>463</v>
       </c>
       <c r="O23" s="6">
         <f t="shared" si="1"/>
@@ -16481,16 +17084,16 @@
       </c>
       <c r="E24" s="54"/>
       <c r="F24" s="42" t="s">
-        <v>458</v>
+        <v>482</v>
       </c>
       <c r="G24" s="43" t="s">
-        <v>464</v>
+        <v>488</v>
       </c>
       <c r="H24" s="51">
         <v>45799.734027777777</v>
       </c>
       <c r="I24" s="42" t="s">
-        <v>436</v>
+        <v>460</v>
       </c>
       <c r="J24" s="42">
         <v>1</v>
@@ -16500,7 +17103,7 @@
         <v>1</v>
       </c>
       <c r="N24" s="42" t="s">
-        <v>465</v>
+        <v>489</v>
       </c>
       <c r="O24" s="6">
         <f t="shared" si="1"/>
@@ -16520,16 +17123,16 @@
       </c>
       <c r="E25" s="54"/>
       <c r="F25" s="42" t="s">
-        <v>458</v>
+        <v>482</v>
       </c>
       <c r="G25" s="43" t="s">
-        <v>466</v>
+        <v>490</v>
       </c>
       <c r="H25" s="51">
         <v>45796.43472222222</v>
       </c>
       <c r="I25" s="42" t="s">
-        <v>436</v>
+        <v>460</v>
       </c>
       <c r="J25" s="42">
         <v>1</v>
@@ -16539,7 +17142,7 @@
         <v>1</v>
       </c>
       <c r="N25" s="42" t="s">
-        <v>467</v>
+        <v>491</v>
       </c>
       <c r="O25" s="6">
         <f t="shared" si="1"/>
@@ -16559,16 +17162,16 @@
       </c>
       <c r="E26" s="54"/>
       <c r="F26" s="42" t="s">
-        <v>458</v>
+        <v>482</v>
       </c>
       <c r="G26" s="43" t="s">
-        <v>468</v>
+        <v>492</v>
       </c>
       <c r="H26" s="51">
         <v>45799.745138888888</v>
       </c>
       <c r="I26" s="42" t="s">
-        <v>436</v>
+        <v>460</v>
       </c>
       <c r="J26" s="42">
         <v>1</v>
@@ -16578,7 +17181,7 @@
         <v>1</v>
       </c>
       <c r="N26" s="42" t="s">
-        <v>469</v>
+        <v>493</v>
       </c>
       <c r="O26" s="6">
         <f t="shared" si="1"/>
@@ -16598,16 +17201,16 @@
       </c>
       <c r="E27" s="54"/>
       <c r="F27" s="42" t="s">
-        <v>431</v>
+        <v>455</v>
       </c>
       <c r="G27" s="43" t="s">
-        <v>470</v>
+        <v>494</v>
       </c>
       <c r="H27" s="51">
         <v>45826.443749999999</v>
       </c>
       <c r="I27" s="42" t="s">
-        <v>436</v>
+        <v>460</v>
       </c>
       <c r="J27" s="42">
         <v>1</v>
@@ -16617,7 +17220,7 @@
         <v>1</v>
       </c>
       <c r="N27" s="42" t="s">
-        <v>471</v>
+        <v>495</v>
       </c>
       <c r="O27" s="6">
         <f t="shared" si="1"/>
@@ -16637,16 +17240,16 @@
       </c>
       <c r="E28" s="59"/>
       <c r="F28" s="60" t="s">
-        <v>431</v>
+        <v>455</v>
       </c>
       <c r="G28" s="61" t="s">
-        <v>472</v>
+        <v>496</v>
       </c>
       <c r="H28" s="62">
         <v>45826.444444444445</v>
       </c>
       <c r="I28" s="60" t="s">
-        <v>436</v>
+        <v>460</v>
       </c>
       <c r="J28" s="60">
         <v>1</v>
@@ -16657,7 +17260,7 @@
         <v>1</v>
       </c>
       <c r="N28" s="60" t="s">
-        <v>434</v>
+        <v>458</v>
       </c>
       <c r="O28" s="63">
         <f t="shared" si="1"/>
@@ -16722,7 +17325,7 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>473</v>
+        <v>497</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>3</v>
@@ -16740,13 +17343,13 @@
         <v>12</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>474</v>
+        <v>498</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>475</v>
+        <v>499</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>425</v>
+        <v>449</v>
       </c>
       <c r="K1" s="3" t="s">
         <v>13</v>
@@ -16755,13 +17358,13 @@
         <v>19</v>
       </c>
       <c r="M1" s="4" t="s">
-        <v>400</v>
+        <v>424</v>
       </c>
       <c r="N1" s="4" t="s">
         <v>15</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>476</v>
+        <v>500</v>
       </c>
     </row>
   </sheetData>
@@ -16809,7 +17412,7 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>473</v>
+        <v>497</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>3</v>
@@ -16827,13 +17430,13 @@
         <v>12</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>474</v>
+        <v>498</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>475</v>
+        <v>499</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>425</v>
+        <v>449</v>
       </c>
       <c r="K1" s="3" t="s">
         <v>13</v>
@@ -16842,13 +17445,13 @@
         <v>19</v>
       </c>
       <c r="M1" s="4" t="s">
-        <v>400</v>
+        <v>424</v>
       </c>
       <c r="N1" s="4" t="s">
         <v>15</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>476</v>
+        <v>500</v>
       </c>
     </row>
   </sheetData>
